--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -928,7 +928,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102683852.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -967,7 +971,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>1.7150/1.6850</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1135,7 +1139,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1148,7 +1154,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>102683850.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1187,7 +1197,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6100</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1368,7 +1378,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>012682365.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>0.73Y</t>
@@ -1588,7 +1602,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102683843.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>7Y</t>
@@ -1795,7 +1813,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -1808,7 +1828,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102683854.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -1847,7 +1871,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7100</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -2015,7 +2039,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -2028,7 +2054,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>012682364.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -2067,7 +2097,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.5600/--</t>
+          <t>1.5600/1.5300</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -2248,7 +2278,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683846.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2287,7 +2321,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7798</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2455,7 +2489,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -2468,7 +2504,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>012682363.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>0.49Y</t>
@@ -2507,7 +2547,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -2688,7 +2728,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102683841.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2727,7 +2771,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.6250/1.5800</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2899,7 +2943,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -2912,7 +2958,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>102683855.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -3136,7 +3186,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102690056.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -3175,7 +3229,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0500</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3356,7 +3410,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>102683849.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -3395,7 +3453,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3567,7 +3625,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -3625,7 +3685,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5700</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3810,7 +3870,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>102683857.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -3849,7 +3913,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -4021,7 +4085,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
@@ -4034,7 +4100,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>102683851.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
@@ -4262,7 +4332,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>102683842.IB</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4301,7 +4375,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/1.6850</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4473,12 +4547,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN006(浮息债券)</t>
+          <t>26越秀集团MTN006</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4486,7 +4562,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>102683856.IB</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4525,7 +4605,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4710,7 +4790,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>102683848.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -4930,7 +5014,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>102683844.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -4969,7 +5057,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.4700</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -5137,7 +5225,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -5150,7 +5240,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>102683853.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -5357,7 +5451,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
@@ -5370,7 +5466,11 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>012682366.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>0.12Y</t>
@@ -5409,7 +5509,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5200</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5577,7 +5677,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -5861,7 +5963,11 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6037,7 +6143,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.6800</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6873,7 +6979,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
@@ -7110,74 +7218,88 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>满坤转债</t>
+          <t>26天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>123287.SZ</t>
+          <t>102683840.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.6</v>
+        <v>1.0</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>2.50 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>25天津创投MTN001(科创债)</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>3.86Y+3.00Y</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2.3549</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>天津创业投资有限公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>09-28 09:00</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>吉安满坤科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:15</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U32" s="3"/>
@@ -7187,51 +7309,55 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>2.45%~2.55%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
+          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7241,54 +7367,54 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2034-09-29</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP32" s="3"/>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7298,7 +7424,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7311,12 +7437,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26天津创投MTN001(科创债)</t>
+          <t>26乐城02</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7324,56 +7452,60 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>284142.SH</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>8Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.00</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25天津创投MTN001(科创债)</t>
+          <t>26乐城01</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>3.86Y+3.00Y</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>1.7117</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.6900</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司</t>
+          <t>乐清市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 17.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7383,7 +7515,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7393,46 +7525,46 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>国信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7442,64 +7574,72 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
+          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2034-09-29</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP33" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7532,49 +7672,43 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN007(浮息债券)</t>
+          <t>满坤转债</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C34" s="3"/>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>123287.SZ</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.0</v>
+        <v>7.6</v>
       </c>
       <c r="F34" s="3"/>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>1.55 ~ 1.85</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>24越秀集团MTN007(绿色)</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7584,14 +7718,10 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.58</t>
-        </is>
-      </c>
+          <t>吉安满坤科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P34" s="3"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7599,7 +7729,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 09:15</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7609,61 +7739,61 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X34" s="3"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
+          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7673,57 +7803,49 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2032-09-28</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="AP34" s="3"/>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7756,128 +7878,142 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>常青转债</t>
+          <t>26越秀集团MTN007</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>113711.SH</t>
+          <t>102683847.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>1.55 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>24越秀集团MTN007(绿色)</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2.91Y</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1.6850</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>1.7000/--</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>广州越秀集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.58</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>09-28 09:00</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>江苏常青树新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:30</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
+          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7887,23 +8023,27 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
@@ -7911,25 +8051,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP35" s="3"/>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7962,53 +8106,43 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26鄂州01</t>
+          <t>常青转债</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>284128.SH</t>
+          <t>113711.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F36" s="3"/>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>24鄂州01</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>175D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6944</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8018,14 +8152,10 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>B- 40.00</t>
-        </is>
-      </c>
+          <t>江苏常青树新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P36" s="3"/>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8033,7 +8163,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:30</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8043,47 +8173,51 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z36" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
+          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8093,17 +8227,17 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2032-09-28</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8114,42 +8248,38 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP36" s="3"/>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8182,7 +8312,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26星乙V1</t>
+          <t>26鄂州01</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8190,33 +8320,45 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C37" s="3"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>284128.SH</t>
+        </is>
+      </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>24鄂州01</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>175D</t>
+        </is>
+      </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6944</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8226,10 +8368,14 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P37" s="3"/>
+          <t>鄂州市新航程基础设施建设有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.00</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8252,34 +8398,38 @@
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>2.25%~2.35%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>湖北省-鄂州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3" t="inlineStr">
-        <is>
-          <t>中合中小企业融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8292,12 +8442,12 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8328,44 +8478,472 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AZ37" s="3"/>
+    </row>
+    <row r="38" customHeight="true" ht="18.0">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>26星乙V1</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>09-28 18:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>江油星乙农业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>四川省-绵阳市</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr">
+        <is>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+        </is>
+      </c>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="AP37" s="3"/>
-      <c r="AQ37" s="3"/>
-      <c r="AR37" s="3"/>
-      <c r="AS37" s="3"/>
-      <c r="AT37" s="3" t="inlineStr">
+      <c r="AP38" s="3"/>
+      <c r="AQ38" s="3"/>
+      <c r="AR38" s="3"/>
+      <c r="AS38" s="3"/>
+      <c r="AT38" s="3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AU37" s="3" t="inlineStr">
+      <c r="AU38" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AV37" s="3" t="inlineStr">
+      <c r="AV38" s="3" t="inlineStr">
         <is>
           <t>有担保</t>
         </is>
       </c>
-      <c r="AW37" s="3" t="inlineStr">
+      <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>不含权</t>
         </is>
       </c>
-      <c r="AX37" s="3" t="inlineStr">
+      <c r="AX38" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY37" s="3" t="inlineStr">
+      <c r="AY38" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ38" s="3"/>
+    </row>
+    <row r="39" customHeight="true" ht="18.0">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>26淮新03</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>09-28 18:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>284161.SH</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>26淮新02</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>1.85Y</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>1.6481</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>1.6900/--</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>淮安新城投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.63</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>09-28 16:00</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-淮安市</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>2028-09-29</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AZ39" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-28" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-29" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26滨江04</t>
+          <t>26桂铁投MTN002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,58 +702,60 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>284047.SH</t>
+          <t>102683852.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.7</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>11.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>11.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>24滨江投资PPN003</t>
+          <t>26桂铁07</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.95Y+2.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.6778</t>
+          <t>1.7092</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司</t>
+          <t>广西铁路投资集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 18.94</t>
+          <t>B- 43.11</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -763,29 +765,33 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -796,23 +802,23 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
+          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -822,32 +828,28 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -857,17 +859,17 @@
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
@@ -877,12 +879,12 @@
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
@@ -892,7 +894,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -902,7 +904,7 @@
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
@@ -915,12 +917,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ3" s="3"/>
+      <c r="AZ3" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26桂铁投MTN002</t>
+          <t>26苏州交投MTN001</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -930,58 +934,60 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683852.IB</t>
+          <t>102683850.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26桂铁07</t>
+          <t>26苏州交投MTN002</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+2.00Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.7116</t>
+          <t>1.6607</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>1.7150/1.6850</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>苏州交通投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 48.71</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -996,7 +1002,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1004,16 +1010,20 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1024,17 +1034,17 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
+          <t>发行人本次发行规模5亿元,所募资金拟用于偿还置换债务融资工具的银行借款,借款主体均为苏州交通投资集团有限责任公司[25苏州交投MTN001]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
@@ -1055,7 +1065,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
+          <t>苏州交通投资集团有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1091,7 +1101,7 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
@@ -1101,22 +1111,22 @@
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV4" s="3" t="inlineStr">
@@ -1126,7 +1136,7 @@
       </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr">
@@ -1139,14 +1149,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26苏州交投MTN001</t>
+          <t>26南京铁建SCP002</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1156,58 +1164,60 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>102683850.IB</t>
+          <t>012682365.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26苏州交投MTN002</t>
+          <t>24南京铁建MTN001</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>1.15Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.6607</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>苏州交通投资集团有限责任公司</t>
+          <t>南京铁路建设投资有限责任公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.94</t>
+          <t>C- 16.35</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1222,7 +1232,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1230,16 +1240,18 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>2.83</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1250,23 +1262,23 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行规模5亿元,所募资金拟用于偿还置换债务融资工具的银行借款,借款主体均为苏州交通投资集团有限责任公司[25苏州交投MTN001]</t>
+          <t>本期发行金额3亿元,拟用于偿还发行人本部有息债务</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,宁波银行股份有限公司</t>
+          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1281,7 +1293,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>苏州交通投资集团有限责任公司2026年度第一期中期票据</t>
+          <t>南京铁路建设投资有限责任公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1291,7 +1303,7 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-06-24</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
@@ -1327,17 +1339,17 @@
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1370,7 +1382,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26南京铁建SCP002</t>
+          <t>26涪陵实业MTN003A</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1380,43 +1392,45 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>012682365.IB</t>
+          <t>102683843.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>24南京铁建MTN001</t>
+          <t>26涪陵实业MTN001</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.15Y</t>
+          <t>6.72Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>2.1488</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1426,12 +1440,12 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>南京铁路建设投资有限责任公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 16.35</t>
+          <t>C 25.04</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1441,7 +1455,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1458,39 +1472,39 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额3亿元,拟用于偿还发行人本部有息债务</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1505,7 +1519,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>南京铁路建设投资有限责任公司2026年度第二期超短期融资券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1515,7 +1529,7 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2027-06-24</t>
+          <t>2033-09-29</t>
         </is>
       </c>
       <c r="AK6" s="3"/>
@@ -1541,27 +1555,27 @@
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1589,12 +1603,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003A</t>
+          <t>26常德城发MTN002</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1604,58 +1620,60 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>102683843.IB</t>
+          <t>102683854.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>24常发01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>6.72Y</t>
+          <t>2.73Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2.1488</t>
+          <t>1.7117</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7100</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>常德市城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>B- 38.58</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1665,12 +1683,12 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1678,8 +1696,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -1687,28 +1709,28 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1729,7 +1751,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)</t>
+          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1739,7 +1761,7 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2033-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
@@ -1760,7 +1782,7 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
@@ -1770,24 +1792,24 @@
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR7" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
           <t/>
@@ -1814,13 +1836,13 @@
         </is>
       </c>
       <c r="AZ7" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26常德城发MTN002</t>
+          <t>26立讯精工SCP008</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1830,58 +1852,60 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683854.IB</t>
+          <t>012682364.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.34 ~ 1.54</t>
         </is>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>24常发01</t>
+          <t>26立讯精工SCP007</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.73Y</t>
+          <t>260D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7153</t>
+          <t>1.5472</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.7100</t>
+          <t>1.5500/1.5300</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.37</t>
+          <t>C+ 34.81</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1905,47 +1929,49 @@
         </is>
       </c>
       <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="V8" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
@@ -1955,7 +1981,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
+          <t>立讯精密工业股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1965,7 +1991,7 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -1986,32 +2012,32 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2039,14 +2065,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ8" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ8" s="3"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP008</t>
+          <t>26创元投资MTN002</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2056,58 +2080,60 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>012682364.IB</t>
+          <t>102683846.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.34 ~ 1.54</t>
+          <t>1.60 ~ 2.00</t>
         </is>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP007</t>
+          <t>26创元投资MTN001</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>260D</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.5472</t>
+          <t>1.8136</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.5600/1.5300</t>
+          <t>1.8300/1.7700</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>苏州创元投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.57</t>
+          <t>C- 14.99</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2122,7 +2148,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2130,48 +2156,52 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>发行人本期债务融资工具发行金额2.50亿元,募集资金拟全部用于发行人本部偿还有息负债</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2181,7 +2211,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第八期超短期融资券</t>
+          <t>苏州创元投资发展(集团)有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2191,7 +2221,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2217,27 +2247,27 @@
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2265,12 +2295,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26创元投资MTN002</t>
+          <t>26杭州钢铁SCP003</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2280,58 +2312,60 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683846.IB</t>
+          <t>012682363.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26创元投资MTN001</t>
+          <t>26杭州钢铁SCP002</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>200D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.8136</t>
+          <t>1.5172</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7798</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>苏州创元投资发展(集团)有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 14.98</t>
+          <t>C- 19.38</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2341,12 +2375,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2354,7 +2388,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>1.62</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
@@ -2363,7 +2399,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2374,23 +2410,23 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额2.50亿元,募集资金拟全部用于发行人本部偿还有息负债</t>
+          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2405,7 +2441,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>苏州创元投资发展(集团)有限公司2026年度第二期中期票据</t>
+          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2415,7 +2451,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2446,22 +2482,22 @@
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2489,14 +2525,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP003</t>
+          <t>26东航股MTN002</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2506,58 +2540,60 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>012682363.IB</t>
+          <t>102683841.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>24.0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>24.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP002</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5172</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 19.38</t>
+          <t>B 52.59</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2572,7 +2608,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2580,16 +2616,18 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2600,28 +2638,28 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
+          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2631,7 +2669,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2641,10 +2679,14 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
-        </is>
-      </c>
-      <c r="AK11" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2667,27 +2709,27 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2715,12 +2757,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN002</t>
+          <t>26厦门航空MTN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2730,7 +2774,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683841.IB</t>
+          <t>102683855.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2739,9 +2783,11 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 1.80</t>
@@ -2751,37 +2797,37 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>26厦门航空MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.6600</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.6250/1.5800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>厦门航空有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.72</t>
+          <t>B- 44.03</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2791,7 +2837,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2804,16 +2850,18 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>2.18</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2824,17 +2872,17 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
+          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2855,7 +2903,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
+          <t>厦门航空有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2895,7 +2943,7 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2943,14 +2991,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN002</t>
+          <t>26九合财金MTN001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2960,58 +3006,60 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683855.IB</t>
+          <t>102690056.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN001(可持续挂钩)</t>
+          <t>25九合财金MTN003</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>3.91Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6600</t>
+          <t>2.0800</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0500</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司</t>
+          <t>淄博市临淄区九合财金控股有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 37.17</t>
+          <t>C 25.55</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3038,33 +3086,33 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
+          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3075,7 +3123,7 @@
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -3085,7 +3133,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司2026年度第二期中期票据</t>
+          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3095,14 +3143,10 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3120,32 +3164,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3178,7 +3222,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26九合财金MTN001</t>
+          <t>26四川港投MTN002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3188,58 +3232,60 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102690056.IB</t>
+          <t>102683849.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25九合财金MTN003</t>
+          <t>25四川港投MTN001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.91Y</t>
+          <t>3.30Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2.0800</t>
+          <t>1.7758</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/2.0500</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司</t>
+          <t>四川省港航投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 25.82</t>
+          <t>C 29.13</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3249,12 +3295,12 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3262,37 +3308,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
+          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3313,7 +3363,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
+          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3323,10 +3373,14 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3349,7 +3403,7 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
@@ -3359,12 +3413,12 @@
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
@@ -3397,12 +3451,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26四川港投MTN002</t>
+          <t>26莱克电气SCP002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3412,58 +3468,60 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683849.IB</t>
+          <t>012682332.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25四川港投MTN001</t>
+          <t>26莱克电气SCP001(绿色)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>3.30Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7758</t>
+          <t>1.5600</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.7800/--</t>
+          <t>--/1.5700</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司</t>
+          <t>莱克电气股份有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 29.13</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3473,7 +3531,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3486,48 +3544,52 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
+          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3537,7 +3599,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3547,12 +3609,12 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2027-03-28</t>
         </is>
       </c>
       <c r="AK15" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL15" s="3" t="inlineStr">
@@ -3572,32 +3634,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>白色家电</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3625,14 +3687,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP002</t>
+          <t>26晋中公用MTN003</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3642,60 +3702,60 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>012682332.IB</t>
+          <t>102683857.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP001(绿色)</t>
+          <t>26晋中01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>2.82Y+2.00Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.5600</t>
+          <t>1.7164</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/1.5700</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>D+ 7.23</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3710,7 +3770,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3718,48 +3778,50 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>2.55</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>山西省-晋中市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
+          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3769,7 +3831,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3779,12 +3841,12 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-03-28</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL16" s="3" t="inlineStr">
@@ -3804,32 +3866,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>白色家电</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3857,12 +3919,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26晋中公用MTN003</t>
+          <t>26鲁能源MTN003(科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3872,58 +3936,60 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683857.IB</t>
+          <t>102683851.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26晋中01</t>
+          <t>26鲁能源MTN002(科创债)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.82Y+2.00Y</t>
+          <t>2.93Y+N</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7218</t>
+          <t>1.7277</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.23</t>
+          <t>B- 41.55</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3938,7 +4004,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -3946,37 +4012,43 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>3.3</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z17" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>山西省-晋中市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
+          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -3997,7 +4069,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
+          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4032,32 +4104,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4072,12 +4144,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4085,14 +4157,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN003(科创债)</t>
+          <t>26凤城河MTN005</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4102,58 +4172,60 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683851.IB</t>
+          <t>102683842.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN002(科创债)</t>
+          <t>26凤城河MTN004</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+N</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7277</t>
+          <t>1.7018</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6950/1.6900</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 42.31</t>
+          <t>C- 19.69</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4163,12 +4235,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4176,41 +4248,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z18" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
+          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4231,7 +4303,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
+          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4266,32 +4338,32 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4306,12 +4378,12 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY18" s="3" t="inlineStr">
@@ -4319,12 +4391,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN005</t>
+          <t>26越秀集团MTN006</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4334,7 +4408,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683842.IB</t>
+          <t>102683856.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -4343,49 +4417,51 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.55 ~ 1.85</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN004</t>
+          <t>24越秀集团MTN007(绿色)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7018</t>
+          <t>1.6850</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.7000/1.6850</t>
+          <t>1.7050/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 16.82</t>
+          <t>C+ 33.56</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4395,12 +4471,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4408,11 +4484,15 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
@@ -4422,23 +4502,23 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4459,7 +4539,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
+          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4494,32 +4574,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4547,14 +4627,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN006</t>
+          <t>26温州现代MTN001</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4564,58 +4642,60 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683856.IB</t>
+          <t>102683848.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 1.85</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>24越秀集团MTN007(绿色)</t>
+          <t>24温州现代MTN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>110D+2.00Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>1.5117</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>温州市现代服务业发展集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.58</t>
+          <t>C+ 34.56</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4630,7 +4710,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4638,16 +4718,20 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.47</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4658,17 +4742,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4689,7 +4773,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
+          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4699,64 +4783,60 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
           <t>2029-09-29</t>
         </is>
       </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO20" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4764,7 +4844,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4782,7 +4862,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26温州现代MTN001</t>
+          <t>26涪陵实业MTN003B</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4792,58 +4872,60 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683848.IB</t>
+          <t>102683844.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>1.75</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24温州现代MTN001</t>
+          <t>26涪陵实业MTN002B</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>110D+2.00Y</t>
+          <t>9.97Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5117</t>
+          <t>2.4907</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.5500/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.59</t>
+          <t>C 25.04</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4853,12 +4935,12 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4866,37 +4948,39 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U21" s="3"/>
+      <c r="U21" s="4" t="n">
+        <v>2.62</v>
+      </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>2.37%~2.47%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -4917,7 +5001,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4927,7 +5011,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -4948,7 +5032,7 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
@@ -4963,22 +5047,22 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
@@ -4988,7 +5072,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5001,12 +5085,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003B</t>
+          <t>26厦门市政MTN002</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5016,58 +5102,60 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102683844.IB</t>
+          <t>102683853.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002B</t>
+          <t>26厦门市政MTN001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>9.97Y</t>
+          <t>2.51Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.4907</t>
+          <t>1.6057</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/2.4700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>厦门市政集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5077,12 +5165,12 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5090,37 +5178,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.37%~2.47%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5141,7 +5233,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种二)</t>
+          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5151,7 +5243,7 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5177,7 +5269,7 @@
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -5226,13 +5318,13 @@
         </is>
       </c>
       <c r="AZ22" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN002</t>
+          <t>26夏商SCP029</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5242,58 +5334,60 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683853.IB</t>
+          <t>012682366.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F23" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.30 ~ 1.51</t>
         </is>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN001</t>
+          <t>26夏商SCP025</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6057</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>B 51.36</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5303,12 +5397,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5316,21 +5410,25 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
+      <c r="U23" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
@@ -5341,18 +5439,18 @@
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
+          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5367,7 +5465,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5377,7 +5475,7 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5398,32 +5496,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5452,13 +5550,13 @@
         </is>
       </c>
       <c r="AZ23" s="4" t="n">
-        <v>0.0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP029</t>
+          <t>26余杭城投PPN003</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5466,60 +5564,56 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>012682366.IB</t>
-        </is>
-      </c>
+      <c r="C24" s="3"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP025</t>
+          <t>26余杭城投PPN002</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.7160</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>杭州余杭城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C 29.86</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5534,7 +5628,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5542,43 +5636,47 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
+          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5593,17 +5691,17 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
+          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5624,37 +5722,37 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5664,7 +5762,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5677,14 +5775,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26星乙V2</t>
+          <t>26洞庭实业PPN002</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5699,26 +5795,34 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>26洞庭实业PPN001</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>4.75Y</t>
+        </is>
+      </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.1752</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5728,10 +5832,14 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3"/>
+          <t>湖南洞庭新实业集团有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>D+ 7.53</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5739,7 +5847,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5754,8 +5862,16 @@
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5764,27 +5880,23 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>湖南省-岳阳市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>东兴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5794,12 +5906,12 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
+          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5815,41 +5927,57 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO25" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP25" s="3"/>
-      <c r="AQ25" s="3"/>
-      <c r="AR25" s="3"/>
-      <c r="AS25" s="3"/>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -5872,7 +6000,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26科集01</t>
+          <t>26南宁高新PPN002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5880,45 +6008,41 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>520510.SZ</t>
-        </is>
-      </c>
+      <c r="C26" s="3"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.0</v>
+        <v>4.5</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.90 ~ 2.30</t>
         </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>23创集K2</t>
+          <t>26南高K1</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>85D+2.00Y</t>
+          <t>4.63Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5152</t>
+          <t>1.9599</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5928,12 +6052,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司</t>
+          <t>南宁高新产业建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D- 1.80</t>
+          <t>D+ 7.69</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5943,29 +6067,33 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -5976,23 +6104,23 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
+          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6002,12 +6130,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6017,60 +6145,60 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>房地产服务</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>其他房地产服务</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6091,12 +6219,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN003</t>
+          <t>26天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6104,56 +6234,62 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102683840.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.50 ~ 3.00</t>
         </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN002</t>
+          <t>25天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>3.86Y+3.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7160</t>
+          <t>2.3549</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.6800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司</t>
+          <t>天津创业投资有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 29.47</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6168,7 +6304,7 @@
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -6176,43 +6312,51 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
+      <c r="U27" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z27" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
+          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6227,17 +6371,17 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2034-09-29</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6258,37 +6402,33 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP27" s="3"/>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6311,54 +6451,64 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ27" s="3"/>
+      <c r="AZ27" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26龙翔01</t>
+          <t>26缙资03</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C28" s="3"/>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>284127.SH</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
+        <v>7.1</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>47.1</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25射阳02</t>
+          <t>26缙资02</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3.39Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7925</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6368,12 +6518,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司</t>
+          <t>缙云县国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C+ 30.52</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6393,45 +6543,45 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.28%~2.38%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>长春新区发展集团有限公司</t>
+          <t>缙云县国有资本运营有限公司</t>
         </is>
       </c>
       <c r="AE28" s="3" t="inlineStr">
@@ -6446,12 +6596,12 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6461,12 +6611,12 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
         <is>
-          <t>休8</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL28" s="3" t="inlineStr">
@@ -6481,37 +6631,37 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>生物制品</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6544,64 +6694,72 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN002</t>
+          <t>26淮新03</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>284161.SH</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.5</v>
+        <v>13.7</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>35.84</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN001</t>
+          <t>26淮新02</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>1.85Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2.1752</t>
+          <t>1.6449</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司</t>
+          <t>淮安新城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.53</t>
+          <t>C- 23.26</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6611,7 +6769,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6628,12 +6786,12 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6644,23 +6802,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>湖南省-岳阳市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
+          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6670,12 +6828,12 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6685,13 +6843,13 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6706,32 +6864,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6764,64 +6922,72 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26南宁高新PPN002</t>
+          <t>26乐城02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C30" s="3"/>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>284142.SH</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.5</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>44.1</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26南高K1</t>
+          <t>26乐城01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>4.63Y</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.9493</t>
+          <t>1.7085</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6900</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司</t>
+          <t>乐清市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.59</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6831,7 +6997,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6841,19 +7007,19 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -6864,23 +7030,23 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>国信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -6890,12 +7056,12 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6905,33 +7071,37 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
@@ -6941,12 +7111,12 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
@@ -6979,60 +7149,62 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ30" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ30" s="3"/>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26缙资03</t>
+          <t>26鄂州01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-28 17:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>284127.SH</t>
+          <t>284128.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.1</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>77.98</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26缙资02</t>
+          <t>24鄂州01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>175D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7937</t>
+          <t>1.6991</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7042,12 +7214,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司</t>
+          <t>鄂州市新航程基础设施建设有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.52</t>
+          <t>B- 40.00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7074,12 +7246,12 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7090,24 +7262,20 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>湖北省-鄂州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD31" s="3" t="inlineStr">
-        <is>
-          <t>缙云县国有资本运营有限公司</t>
-        </is>
-      </c>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -7125,7 +7293,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7135,14 +7303,10 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7160,27 +7324,27 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
@@ -7195,7 +7359,7 @@
       </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW31" s="3" t="inlineStr">
@@ -7218,53 +7382,57 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26天津创投MTN001(科创债)</t>
+          <t>26滨江04</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683840.IB</t>
+          <t>284047.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.0</v>
+        <v>9.7</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>36.1</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25天津创投MTN001(科创债)</t>
+          <t>24滨江投资PPN003</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3.86Y+3.00Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>1.6778</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7274,12 +7442,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司</t>
+          <t>南京滨江投资发展有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 18.94</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7289,7 +7457,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7299,50 +7467,46 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7352,69 +7516,77 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
+          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2034-09-29</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP32" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7424,7 +7596,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7437,77 +7609,63 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26乐城02</t>
+          <t>满坤转债</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>284142.SH</t>
+          <t>123287.SZ</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.0</v>
+        <v>7.6</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>-125.9</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>26乐城01</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>2.82Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7117</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>C- 17.00</t>
-        </is>
-      </c>
+          <t>吉安满坤科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3"/>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7515,7 +7673,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:15</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7525,78 +7683,74 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t>1.73%~1.83%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X33" s="3"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
+          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,平安证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2032-09-28</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7604,7 +7758,7 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7614,32 +7768,28 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3"/>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7672,128 +7822,144 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>满坤转债</t>
+          <t>26越秀集团MTN007</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>123287.SZ</t>
+          <t>102683847.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4" t="n">
-        <v>0.2</v>
-      </c>
+        <v>7.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>1.55 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>24越秀集团MTN007(绿色)</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>2.91Y</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1.6850</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>1.7050/--</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>广州越秀集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.56</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>09-28 09:00</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>吉安满坤科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:15</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7803,23 +7969,27 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO34" s="3" t="inlineStr">
@@ -7827,25 +7997,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP34" s="3"/>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7878,70 +8052,58 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN007</t>
+          <t>常青转债</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683847.IB</t>
+          <t>113711.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>1.55 ~ 1.85</t>
-        </is>
-      </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>-125.9</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>24越秀集团MTN007(绿色)</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.58</t>
-        </is>
-      </c>
+          <t>江苏常青树新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7949,7 +8111,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 09:30</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7959,61 +8121,61 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X35" s="3"/>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z35" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
+          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8023,57 +8185,49 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2032-09-28</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="AP35" s="3"/>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8106,138 +8260,156 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>常青转债</t>
+          <t>26科集01</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>520510.SZ</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>23创集K2</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>85D+2.00Y</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1.5161</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>惠州大亚湾科创集团有限公司</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>D- 1.80</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
           <t>09-28 15:00</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>113711.SH</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>6Y</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="S36" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>江苏常青树新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:30</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
+          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
+          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8248,12 +8420,12 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
@@ -8261,25 +8433,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP36" s="3"/>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8312,17 +8488,17 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26鄂州01</t>
+          <t>26星乙V1</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284128.SH</t>
+          <t>520508.SZ</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -8331,34 +8507,30 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>83.98</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>24鄂州01</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>175D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6944</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8368,14 +8540,10 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>B- 40.00</t>
-        </is>
-      </c>
+          <t>江油星乙农业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8400,36 +8568,36 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X37" s="3" t="inlineStr">
-        <is>
-          <t>2.25%~2.35%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X37" s="3"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE37" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8442,12 +8610,12 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8478,32 +8646,16 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP37" s="3"/>
+      <c r="AQ37" s="3"/>
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="3"/>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8513,7 +8665,7 @@
       </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
@@ -8536,78 +8688,106 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26星乙V1</t>
+          <t>26龙翔01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C38" s="3"/>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>520506.SZ</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+          <t>2.20 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>91.1</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>25射阳02</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>3.39Y</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.7968</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>龙翔投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>09-28 15:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>2.28%~2.38%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8616,22 +8796,22 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
+          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3" t="inlineStr">
         <is>
-          <t>中合中小企业融资担保股份有限公司</t>
+          <t>长春新区发展集团有限公司</t>
         </is>
       </c>
       <c r="AE38" s="3" t="inlineStr">
@@ -8651,7 +8831,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8661,10 +8841,14 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8677,21 +8861,37 @@
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP38" s="3"/>
-      <c r="AQ38" s="3"/>
-      <c r="AR38" s="3"/>
-      <c r="AS38" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>生物制品</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8724,70 +8924,62 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26淮新03</t>
+          <t>26星乙V2</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>284161.SH</t>
+          <t>520509.SZ</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>13.7</v>
+        <v>1.2</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>70.98</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>26淮新02</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>1.85Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6481</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>C- 23.63</t>
-        </is>
-      </c>
+          <t>江油星乙农业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P39" s="3"/>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8795,7 +8987,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-28 16:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8812,14 +9004,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t>1.76%~1.86%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X39" s="3"/>
       <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8828,20 +9016,24 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD39" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE39" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8854,12 +9046,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8869,7 +9061,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -8890,32 +9082,16 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ39" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR39" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
+      <c r="AS39" s="3"/>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -8925,7 +9101,7 @@
       </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW39" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -721,8 +721,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>30.98</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -745,7 +749,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -779,7 +783,7 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>1.5</v>
+        <v>2.5273</v>
       </c>
       <c r="V3" s="4" t="n">
         <v>32.0</v>
@@ -953,8 +957,12 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>23.98</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -1183,8 +1191,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>17.7</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1610,7 +1622,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26常德城发MTN002</t>
+          <t>26立讯精工SCP008</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1620,60 +1632,64 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>102683854.IB</t>
+          <t>012682364.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.5</v>
+        <v>10.0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.5</v>
+        <v>10.0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+          <t>1.34 ~ 1.54</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>22.7</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>24常发01</t>
+          <t>26立讯精工SCP007</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.73Y</t>
+          <t>260D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.7117</t>
+          <t>1.5472</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.7100</t>
+          <t>1.5500/1.5300</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 38.58</t>
+          <t>C+ 34.81</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1688,7 +1704,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1696,52 +1712,50 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n">
-        <v>2.92</v>
-      </c>
+      <c r="U7" s="3"/>
       <c r="V7" s="4" t="n">
-        <v>1.4</v>
+        <v>1.0</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
@@ -1751,7 +1765,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
+          <t>立讯精密工业股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1761,7 +1775,7 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
@@ -1782,32 +1796,32 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1835,14 +1849,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP008</t>
+          <t>26杭州钢铁SCP003</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1852,60 +1864,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>012682364.IB</t>
+          <t>012682363.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.34 ~ 1.54</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+          <t>1.20 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>16.48</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP007</t>
+          <t>26杭州钢铁SCP002</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>260D</t>
+          <t>200D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5472</t>
+          <t>1.5172</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.5500/1.5300</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.81</t>
+          <t>C- 19.38</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1915,12 +1931,12 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1928,39 +1944,39 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U8" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1971,7 +1987,7 @@
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
@@ -1981,7 +1997,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第八期超短期融资券</t>
+          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1991,7 +2007,7 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -2017,27 +2033,27 @@
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2070,7 +2086,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26创元投资MTN002</t>
+          <t>26东航股MTN002</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2080,60 +2096,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683846.IB</t>
+          <t>102683841.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.5</v>
+        <v>24.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.5</v>
+        <v>24.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>24.1</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26创元投资MTN001</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.8136</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7700</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>苏州创元投资发展(集团)有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 14.99</t>
+          <t>B 52.59</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2143,12 +2163,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2157,19 +2177,17 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2180,17 +2198,17 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额2.50亿元,募集资金拟全部用于发行人本部偿还有息负债</t>
+          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
@@ -2201,7 +2219,7 @@
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2211,7 +2229,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>苏州创元投资发展(集团)有限公司2026年度第二期中期票据</t>
+          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2221,10 +2239,14 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK9" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2247,27 +2269,27 @@
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2302,7 +2324,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP003</t>
+          <t>26厦门航空MTN002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2312,60 +2334,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>012682363.IB</t>
+          <t>102683855.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>29.1</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP002</t>
+          <t>26厦门航空MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5172</t>
+          <t>1.6600</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>厦门航空有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 19.38</t>
+          <t>B- 44.03</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2375,12 +2401,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2389,17 +2415,17 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.62</v>
+        <v>2.18</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2410,28 +2436,28 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
+          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2441,7 +2467,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>厦门航空有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2451,10 +2477,14 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2477,27 +2507,27 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2530,7 +2560,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN002</t>
+          <t>26九合财金MTN001</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2540,60 +2570,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683841.IB</t>
+          <t>102690056.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>24.0</v>
+        <v>10.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>24.0</v>
+        <v>10.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+          <t>2.20 ~ 3.20</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>78.98</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>25九合财金MTN003</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>3.91Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>2.0800</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>--/2.0500</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>淄博市临淄区九合财金控股有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B 52.59</t>
+          <t>C 25.55</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2603,12 +2637,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2617,38 +2651,38 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
+          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2659,7 +2693,7 @@
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2669,7 +2703,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
+          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2679,14 +2713,10 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2704,32 +2734,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2757,14 +2787,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ11" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ11" s="3"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN002</t>
+          <t>26四川港投MTN002</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2774,7 +2802,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683855.IB</t>
+          <t>102683849.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2783,51 +2811,55 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.40 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>41.1</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN001(可持续挂钩)</t>
+          <t>25四川港投MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>3.30Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6600</t>
+          <t>1.7758</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司</t>
+          <t>四川省港航投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 44.03</t>
+          <t>C 29.13</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2837,12 +2869,12 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2851,17 +2883,19 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V12" s="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2872,17 +2906,17 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
+          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2893,7 +2927,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2903,7 +2937,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司2026年度第二期中期票据</t>
+          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2938,32 +2972,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2991,12 +3025,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26九合财金MTN001</t>
+          <t>26晋中公用MTN003</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3006,60 +3042,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102690056.IB</t>
+          <t>102683857.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>43.1</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25九合财金MTN003</t>
+          <t>26晋中01</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.91Y</t>
+          <t>2.82Y+2.00Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2.0800</t>
+          <t>1.7164</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/2.0500</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 25.55</t>
+          <t>D+ 7.23</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3074,7 +3114,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3082,16 +3122,18 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="4" t="n">
+        <v>2.55</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3102,17 +3144,17 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>山西省-晋中市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
+          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3133,7 +3175,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3143,10 +3185,14 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3169,7 +3215,7 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3189,7 +3235,7 @@
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3217,12 +3263,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ13" s="3"/>
+      <c r="AZ13" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26四川港投MTN002</t>
+          <t>26鲁能源MTN003(科创债)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3232,60 +3280,60 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683849.IB</t>
+          <t>102683851.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25四川港投MTN001</t>
+          <t>26鲁能源MTN002(科创债)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>3.30Y</t>
+          <t>2.93Y+N</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7758</t>
+          <t>1.7277</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 29.13</t>
+          <t>B- 41.55</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3295,7 +3343,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3309,19 +3357,17 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3329,20 +3375,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z14" s="3"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
+          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3363,7 +3413,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3398,32 +3448,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3438,12 +3488,12 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY14" s="3" t="inlineStr">
@@ -3451,14 +3501,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP002</t>
+          <t>26凤城河MTN005</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3468,60 +3516,64 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>012682332.IB</t>
+          <t>102683842.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+          <t>1.40 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>39.1</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP001(绿色)</t>
+          <t>26凤城河MTN004</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5600</t>
+          <t>1.7018</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.5700</t>
+          <t>1.6950/1.6900</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 19.69</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3531,12 +3583,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3545,51 +3597,51 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.1</v>
+        <v>3.83</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
+          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3599,7 +3651,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
+          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3609,12 +3661,12 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2027-03-28</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK15" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL15" s="3" t="inlineStr">
@@ -3634,7 +3686,7 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
@@ -3644,22 +3696,22 @@
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>白色家电</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3687,12 +3739,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26晋中公用MTN003</t>
+          <t>26越秀集团MTN006</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3702,7 +3756,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683857.IB</t>
+          <t>102683856.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3711,51 +3765,55 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+          <t>1.55 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>35.1</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26晋中01</t>
+          <t>24越秀集团MTN007(绿色)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.82Y+2.00Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7164</t>
+          <t>1.6850</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>1.7050/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.23</t>
+          <t>C+ 33.56</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3770,7 +3828,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3779,38 +3837,40 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V16" s="3"/>
+        <v>1.69</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>山西省-晋中市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3831,7 +3891,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
+          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3866,12 +3926,12 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
@@ -3881,17 +3941,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3919,14 +3979,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN003(科创债)</t>
+          <t>26温州现代MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3936,45 +3994,49 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683851.IB</t>
+          <t>102683848.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>18.98</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN002(科创债)</t>
+          <t>24温州现代MTN001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+N</t>
+          <t>110D+2.00Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7277</t>
+          <t>1.5117</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3984,12 +4046,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
+          <t>温州市现代服务业发展集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 41.55</t>
+          <t>C+ 34.56</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4004,7 +4066,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4015,15 +4077,17 @@
       <c r="U17" s="4" t="n">
         <v>3.3</v>
       </c>
-      <c r="V17" s="3"/>
+      <c r="V17" s="4" t="n">
+        <v>1.47</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4031,24 +4095,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
+          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4069,7 +4129,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
+          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4079,64 +4139,60 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t>2029-09-29</t>
         </is>
       </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4144,12 +4200,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4162,7 +4218,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN005</t>
+          <t>26涪陵实业MTN003B</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4172,60 +4228,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683842.IB</t>
+          <t>102683844.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.0</v>
+        <v>1.75</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.0</v>
+        <v>3.25</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+          <t>1.80 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>77.1</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN004</t>
+          <t>26涪陵实业MTN002B</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>9.97Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7018</t>
+          <t>2.4907</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.6950/1.6900</t>
+          <t>2.5500/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 19.69</t>
+          <t>C 25.04</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4235,12 +4295,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4249,19 +4309,17 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>1.25</v>
-      </c>
+        <v>2.62</v>
+      </c>
+      <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.37%~2.47%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4272,17 +4330,17 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4303,7 +4361,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4313,14 +4371,10 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2036-09-29</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -4348,22 +4402,22 @@
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4398,7 +4452,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN006</t>
+          <t>26厦门市政MTN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4408,60 +4462,64 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683856.IB</t>
+          <t>102683853.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 1.85</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>23.98</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>24越秀集团MTN007(绿色)</t>
+          <t>26厦门市政MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>2.51Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>1.6057</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.7050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>厦门市政集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.56</t>
+          <t>C+ 32.28</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4471,12 +4529,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4485,19 +4543,19 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.69</v>
+        <v>3.0</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4508,17 +4566,17 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4539,7 +4597,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
+          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4549,14 +4607,10 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -4574,12 +4628,12 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4589,17 +4643,17 @@
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4627,12 +4681,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26温州现代MTN001</t>
+          <t>26夏商SCP029</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4642,12 +4698,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683848.IB</t>
+          <t>012682366.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -4658,44 +4714,48 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.30 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>39.03</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>24温州现代MTN001</t>
+          <t>26夏商SCP025</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>110D+2.00Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5117</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.56</t>
+          <t>B 51.36</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4710,7 +4770,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4719,46 +4779,46 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.47</v>
+        <v>1.0</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
+          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4773,7 +4833,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4783,7 +4843,7 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4809,22 +4869,22 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
@@ -4834,7 +4894,7 @@
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV20" s="3" t="inlineStr">
@@ -4844,7 +4904,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4857,12 +4917,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ20" s="3"/>
+      <c r="AZ20" s="4" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003B</t>
+          <t>26余杭城投PPN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4870,62 +4932,60 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>102683844.IB</t>
-        </is>
-      </c>
+      <c r="C21" s="3"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>1.75</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>29.98</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002B</t>
+          <t>26余杭城投PPN002</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>9.97Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2.4907</t>
+          <t>1.7160</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>2.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>杭州余杭城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 25.04</t>
+          <t>C 29.86</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4935,12 +4995,12 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4949,44 +5009,46 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V21" s="3"/>
+        <v>3.67</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>2.37%~2.47%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5001,17 +5063,17 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种二)</t>
+          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -5042,27 +5104,27 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
@@ -5072,7 +5134,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5085,14 +5147,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ21" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ21" s="3"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN002</t>
+          <t>26洞庭实业PPN002</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5100,47 +5160,45 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>102683853.IB</t>
-        </is>
-      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>2.00 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>95.98</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN001</t>
+          <t>26洞庭实业PPN001</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6057</t>
+          <t>2.1752</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5150,12 +5208,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司</t>
+          <t>湖南洞庭新实业集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>D+ 7.53</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5165,12 +5223,12 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5178,47 +5236,43 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U22" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>1.02</v>
-      </c>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>湖南省-岳阳市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
+          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
+          <t>东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5233,12 +5287,12 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
+          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
@@ -5264,12 +5318,12 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
@@ -5317,14 +5371,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP029</t>
+          <t>26南宁高新PPN002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5332,62 +5384,60 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>012682366.IB</t>
-        </is>
-      </c>
+      <c r="C23" s="3"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.90 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>56.98</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP025</t>
+          <t>26南高K1</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>4.63Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.9599</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>南宁高新产业建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B 51.36</t>
+          <t>D+ 7.69</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5402,7 +5452,7 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5411,19 +5461,19 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -5434,12 +5484,12 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
+          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
@@ -5450,7 +5500,7 @@
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5465,17 +5515,17 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
+          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
@@ -5496,32 +5546,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5550,13 +5600,13 @@
         </is>
       </c>
       <c r="AZ23" s="4" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN003</t>
+          <t>26天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5564,41 +5614,51 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>102683840.IB</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>2.50 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>129.17</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN002</t>
+          <t>25天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>3.86Y+3.00Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7160</t>
+          <t>2.3549</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5608,12 +5668,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司</t>
+          <t>天津创业投资有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 29.86</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5628,7 +5688,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5637,46 +5697,50 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.67</v>
+        <v>1.1</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.2</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z24" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
+          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5691,17 +5755,17 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2034-09-29</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
@@ -5722,37 +5786,33 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP24" s="3"/>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5775,54 +5835,64 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN002</t>
+          <t>26缙资03</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C25" s="3"/>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>284127.SH</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>47.1</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN001</t>
+          <t>26缙资02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>2.1752</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5832,12 +5902,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司</t>
+          <t>缙云县国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.53</t>
+          <t>C+ 30.52</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5847,7 +5917,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5864,39 +5934,43 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>湖南省-岳阳市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3"/>
+          <t>浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>缙云县国有资本运营有限公司</t>
+        </is>
+      </c>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5906,12 +5980,12 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5921,13 +5995,17 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5942,12 +6020,12 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -5967,7 +6045,7 @@
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5977,7 +6055,7 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -6000,64 +6078,72 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26南宁高新PPN002</t>
+          <t>26淮新03</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C26" s="3"/>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>284161.SH</t>
+        </is>
+      </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.5</v>
+        <v>13.7</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>35.84</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26南高K1</t>
+          <t>26淮新02</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>4.63Y</t>
+          <t>1.85Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.9599</t>
+          <t>1.6449</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司</t>
+          <t>淮安新城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.69</t>
+          <t>C- 23.26</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6067,12 +6153,12 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 16:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6080,20 +6166,16 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>1.06</v>
-      </c>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -6104,23 +6186,23 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
+          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6130,12 +6212,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6145,13 +6227,13 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM26" s="3" t="inlineStr">
@@ -6171,7 +6253,7 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6181,12 +6263,12 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
@@ -6219,77 +6301,77 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ26" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ26" s="3"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26天津创投MTN001(科创债)</t>
+          <t>26乐城02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683840.IB</t>
+          <t>284142.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>44.1</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>25天津创投MTN001(科创债)</t>
+          <t>26乐城01</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.86Y+3.00Y</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>1.7085</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6900</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司</t>
+          <t>乐清市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6299,33 +6381,29 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6333,30 +6411,26 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>国信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6366,69 +6440,77 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
+          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2034-09-29</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP27" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV27" s="3" t="inlineStr">
@@ -6438,7 +6520,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6451,14 +6533,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26缙资03</t>
+          <t>26鄂州01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6468,47 +6548,47 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284127.SH</t>
+          <t>284128.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.1</v>
+        <v>10.0</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>47.1</v>
+        <v>77.98</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26缙资02</t>
+          <t>24鄂州01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>175D</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.6991</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6518,12 +6598,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司</t>
+          <t>鄂州市新航程基础设施建设有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.52</t>
+          <t>B- 40.00</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6550,12 +6630,12 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6566,24 +6646,20 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>湖北省-鄂州市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3" t="inlineStr">
-        <is>
-          <t>缙云县国有资本运营有限公司</t>
-        </is>
-      </c>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -6601,7 +6677,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6611,14 +6687,10 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6636,27 +6708,27 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6671,7 +6743,7 @@
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6694,7 +6766,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26淮新03</t>
+          <t>26滨江04</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6704,62 +6776,62 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284161.SH</t>
+          <t>284047.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>13.7</v>
+        <v>9.7</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>35.84</v>
+        <v>36.1</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26淮新02</t>
+          <t>24滨江投资PPN003</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>1.85Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6449</t>
+          <t>1.6778</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司</t>
+          <t>南京滨江投资发展有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 23.26</t>
+          <t>C- 18.94</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6769,7 +6841,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-28 16:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6779,40 +6851,40 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
+          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6833,7 +6905,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6843,10 +6915,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6859,17 +6935,17 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6879,12 +6955,12 @@
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
@@ -6922,72 +6998,74 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26乐城02</t>
+          <t>26莱克电气SCP002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284142.SH</t>
+          <t>012682332.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>44.1</v>
+        <v>36.48</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26乐城01</t>
+          <t>26莱克电气SCP001(绿色)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.82Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.7085</t>
+          <t>1.5600</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.7400/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司</t>
+          <t>莱克电气股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6997,7 +7075,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7007,81 +7085,85 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
+          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,平安证券股份有限公司</t>
+          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2027-03-28</t>
         </is>
       </c>
       <c r="AK30" s="3" t="inlineStr">
         <is>
-          <t>休8</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7091,12 +7173,12 @@
       </c>
       <c r="AN30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
@@ -7106,22 +7188,22 @@
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>白色家电</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7154,57 +7236,45 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26鄂州01</t>
+          <t>满坤转债</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>284128.SH</t>
+          <t>123287.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
+        <v>7.6</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="4" t="n">
-        <v>2.19</v>
+        <v>0.2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>77.98</v>
+        <v>-125.9</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>24鄂州01</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>175D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6991</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7214,14 +7284,10 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>B- 40.00</t>
-        </is>
-      </c>
+          <t>吉安满坤科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7229,7 +7295,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:15</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7239,71 +7305,71 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t>2.25%~2.35%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X31" s="3"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z31" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
+          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2032-09-28</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -7314,42 +7380,38 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP31" s="3"/>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7382,57 +7444,45 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26滨江04</t>
+          <t>常青转债</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>284047.SH</t>
+          <t>113711.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.7</v>
+        <v>8.0</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
+      <c r="G32" s="3"/>
       <c r="H32" s="4" t="n">
-        <v>1.65</v>
+        <v>0.2</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>36.1</v>
+        <v>-125.9</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>24滨江投资PPN003</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>2.90Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6778</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7442,14 +7492,10 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>C- 18.94</t>
-        </is>
-      </c>
+          <t>江苏常青树新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3"/>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7457,7 +7503,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:30</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7467,51 +7513,51 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t>1.77%~1.87%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X32" s="3"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z32" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
+          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7521,24 +7567,20 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2032-09-28</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7546,7 +7588,7 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
@@ -7556,32 +7598,28 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3"/>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7614,120 +7652,136 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>满坤转债</t>
+          <t>26科集01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>520510.SZ</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>23创集K2</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>85D+2.00Y</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>1.5161</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>惠州大亚湾科创集团有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>D- 1.80</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
           <t>09-28 15:00</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>123287.SZ</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>6Y</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>-125.9</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>吉安满坤科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:15</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
+          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7737,17 +7791,17 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7758,12 +7812,12 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
@@ -7771,25 +7825,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP33" s="3"/>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7822,72 +7880,62 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN007</t>
+          <t>26星乙V1</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683847.IB</t>
+          <t>520508.SZ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 1.85</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>83.98</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>24越秀集团MTN007(绿色)</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.7050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.56</t>
-        </is>
-      </c>
+          <t>江油星乙农业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P34" s="3"/>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7895,7 +7943,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7912,39 +7960,39 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X34" s="3"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7954,32 +8002,28 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -7994,34 +8038,18 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP34" s="3"/>
+      <c r="AQ34" s="3"/>
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="3"/>
+      <c r="AT34" s="3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
       <c r="AU34" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8029,7 +8057,7 @@
       </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8052,143 +8080,167 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>常青转债</t>
+          <t>26龙翔01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>520506.SZ</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>2.20 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>91.1</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>25射阳02</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>3.39Y</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1.7968</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>龙翔投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
           <t>09-28 15:00</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>113711.SH</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>6Y</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>-125.9</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="S35" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>江苏常青树新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:30</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>2.28%~2.38%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3"/>
+          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>长春新区发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
+          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8196,7 +8248,7 @@
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
@@ -8206,28 +8258,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP35" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>生物制品</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8237,7 +8293,7 @@
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
@@ -8260,7 +8316,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26科集01</t>
+          <t>26星乙V2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8270,7 +8326,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>520510.SZ</t>
+          <t>520509.SZ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -8279,7 +8335,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.0</v>
+        <v>1.2</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
@@ -8288,29 +8344,21 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>62.98</v>
+        <v>70.98</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>23创集K2</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>85D+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.5161</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -8320,14 +8368,10 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>D- 1.80</t>
-        </is>
-      </c>
+          <t>江油星乙农业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P36" s="3"/>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8345,21 +8389,17 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t>2.00%~2.10%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X36" s="3"/>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8368,20 +8408,24 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司</t>
-        </is>
-      </c>
-      <c r="AD36" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE36" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8399,7 +8443,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8409,7 +8453,7 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
@@ -8425,37 +8469,21 @@
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ36" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR36" s="3" t="inlineStr">
-        <is>
-          <t>房地产服务</t>
-        </is>
-      </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>其他房地产服务</t>
-        </is>
-      </c>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP36" s="3"/>
+      <c r="AQ36" s="3"/>
+      <c r="AR36" s="3"/>
+      <c r="AS36" s="3"/>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8465,7 +8493,7 @@
       </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW36" s="3" t="inlineStr">
@@ -8488,17 +8516,17 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26星乙V1</t>
+          <t>26创元投资MTN002</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>520508.SZ</t>
+          <t>102683846.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -8507,30 +8535,40 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.00</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>83.98</v>
+        <v>30.98</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>26创元投资MTN001</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>4.93Y</t>
+        </is>
+      </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.8136</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8540,10 +8578,14 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P37" s="3"/>
+          <t>苏州创元投资发展(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>C- 14.99</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8551,12 +8593,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -8564,43 +8606,47 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>发行人本期债务融资工具发行金额2.50亿元,募集资金拟全部用于发行人本部偿还有息负债</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3" t="inlineStr">
-        <is>
-          <t>中合中小企业融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8610,17 +8656,17 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+          <t>苏州创元投资发展(集团)有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
@@ -8631,41 +8677,57 @@
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP37" s="3"/>
-      <c r="AQ37" s="3"/>
-      <c r="AR37" s="3"/>
-      <c r="AS37" s="3"/>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
@@ -8683,62 +8745,66 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26龙翔01</t>
+          <t>26常德城发MTN002</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>520506.SZ</t>
+          <t>102683854.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>91.1</v>
+        <v>35.98</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25射阳02</t>
+          <t>24常发01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>3.39Y</t>
+          <t>2.73Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7968</t>
+          <t>1.7117</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -8748,12 +8814,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司</t>
+          <t>常德市城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 38.58</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8763,60 +8829,60 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>2.28%~2.38%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
+          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3" t="inlineStr">
-        <is>
-          <t>长春新区发展集团有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8826,82 +8892,78 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO38" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ38" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR38" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>生物制品</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -8919,124 +8981,142 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ38" s="3"/>
+      <c r="AZ38" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26星乙V2</t>
+          <t>26越秀集团MTN007</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>520509.SZ</t>
+          <t>102683847.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F39" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.55 ~ 1.85</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>70.98</v>
+        <v>35.1</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>24越秀集团MTN007(绿色)</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>2.91Y</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>1.6850</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>广州越秀集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.56</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>09-28 09:00</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>09-28 15:00</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>1.8143</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X39" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9046,62 +9126,82 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
+          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>房地产开发</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO39" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP39" s="3"/>
-      <c r="AQ39" s="3"/>
-      <c r="AR39" s="3"/>
-      <c r="AS39" s="3"/>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW39" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-29" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-30" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26桂铁投MTN002</t>
+          <t>26苏州交投MTN001</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,64 +702,64 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>102683852.IB</t>
+          <t>102683850.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>30.98</v>
+        <v>23.98</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26桂铁07</t>
+          <t>26苏州交投MTN002</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+2.00Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.7092</t>
+          <t>1.6607</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>苏州交通投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 43.11</t>
+          <t>C 28.12</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>2.5273</v>
+        <v>4.52</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>32.0</v>
+        <v>1.5</v>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -806,17 +806,17 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
+          <t>发行人本次发行规模5亿元,所募资金拟用于偿还置换债务融资工具的银行借款,借款主体均为苏州交通投资集团有限责任公司[25苏州交投MTN001]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD3" s="3"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
+          <t>苏州交通投资集团有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV3" s="3" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr">
@@ -921,14 +921,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ3" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ3" s="3"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26苏州交投MTN001</t>
+          <t>26南京铁建SCP002</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -938,64 +936,64 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683850.IB</t>
+          <t>012682365.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>23.98</v>
+        <v>17.7</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26苏州交投MTN002</t>
+          <t>24南京铁建MTN001</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>1.15Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.6607</t>
+          <t>1.5365</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>苏州交通投资集团有限责任公司</t>
+          <t>南京铁路建设投资有限责任公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 29.88</t>
+          <t>C+ 32.03</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1010,7 +1008,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1019,19 +1017,17 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>4.37</v>
+      </c>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1042,23 +1038,23 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行规模5亿元,所募资金拟用于偿还置换债务融资工具的银行借款,借款主体均为苏州交通投资集团有限责任公司[25苏州交投MTN001]</t>
+          <t>本期发行金额3亿元,拟用于偿还发行人本部有息债务</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,宁波银行股份有限公司</t>
+          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1073,7 +1069,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>苏州交通投资集团有限责任公司2026年度第一期中期票据</t>
+          <t>南京铁路建设投资有限责任公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1083,7 +1079,7 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-06-24</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1119,17 +1115,17 @@
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1162,7 +1158,7 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26南京铁建SCP002</t>
+          <t>26立讯精工SCP008</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1172,64 +1168,64 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>012682365.IB</t>
+          <t>012682364.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.34 ~ 1.54</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>17.7</v>
+        <v>22.7</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>24南京铁建MTN001</t>
+          <t>26立讯精工SCP007</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>1.15Y</t>
+          <t>260D</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.5365</t>
+          <t>1.5472</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/1.5300</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>南京铁路建设投资有限责任公司</t>
+          <t>立讯精密工业股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 16.35</t>
+          <t>C+ 33.44</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1244,7 +1240,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1253,38 +1249,40 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>1.02</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额3亿元,拟用于偿还发行人本部有息债务</t>
+          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
@@ -1295,7 +1293,7 @@
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
@@ -1305,7 +1303,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>南京铁路建设投资有限责任公司2026年度第二期超短期融资券</t>
+          <t>立讯精密工业股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1315,7 +1313,7 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2027-06-24</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
@@ -1336,32 +1334,32 @@
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1394,7 +1392,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003A</t>
+          <t>26晋中公用MTN003</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1404,60 +1402,64 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683843.IB</t>
+          <t>102683857.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>43.1</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>26晋中01</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>6.72Y</t>
+          <t>2.82Y+2.00Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>2.1488</t>
+          <t>1.7164</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C 25.04</t>
+          <t>D+ 6.98</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1467,12 +1469,12 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1480,16 +1482,18 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>2.55</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1500,17 +1504,17 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>山西省-晋中市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1541,10 +1545,14 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2033-09-29</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1567,7 +1575,7 @@
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
@@ -1587,7 +1595,7 @@
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1622,7 +1630,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP008</t>
+          <t>26夏商SCP029</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1632,64 +1640,64 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>012682364.IB</t>
+          <t>012682366.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.34 ~ 1.54</t>
+          <t>1.30 ~ 1.51</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22.7</v>
+        <v>39.03</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26立讯精工SCP007</t>
+          <t>26夏商SCP025</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>260D</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.5472</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.5500/1.5300</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.81</t>
+          <t>B- 49.42</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1712,7 +1720,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>2.8</v>
+      </c>
       <c r="V7" s="4" t="n">
         <v>1.0</v>
       </c>
@@ -1723,7 +1733,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1734,12 +1744,12 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为10亿元，拟用于偿还发行人存量有息债务</t>
+          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
@@ -1755,7 +1765,7 @@
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
@@ -1765,7 +1775,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>立讯精密工业股份有限公司2026年度第八期超短期融资券</t>
+          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1775,7 +1785,7 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
@@ -1801,27 +1811,27 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1849,79 +1859,79 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP003</t>
+          <t>26乐城02</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>012682363.IB</t>
+          <t>284142.SH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16.48</v>
+        <v>44.1</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP002</t>
+          <t>26乐城01</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5172</t>
+          <t>1.7085</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>1.7400/1.6900</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>乐清市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 19.38</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1931,22 +1941,20 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>1.62</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
@@ -1955,34 +1963,34 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>国信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1992,68 +2000,72 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
-        </is>
-      </c>
-      <c r="AK8" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2086,17 +2098,17 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN002</t>
+          <t>26滨江04</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683841.IB</t>
+          <t>284047.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2105,55 +2117,53 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>24.0</v>
-      </c>
+        <v>9.7</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>24.1</v>
+        <v>36.1</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>24滨江投资PPN003</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.6778</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>南京滨江投资发展有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B 52.59</t>
+          <t>C- 18.75</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2163,31 +2173,29 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>1.7</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2198,98 +2206,98 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
+          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="AK9" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休8</t>
         </is>
       </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2317,14 +2325,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN002</t>
+          <t>26莱克电气SCP002</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2334,64 +2340,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683855.IB</t>
+          <t>012682332.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>29.1</v>
+        <v>36.48</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN001(可持续挂钩)</t>
+          <t>26莱克电气SCP001(绿色)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6600</t>
+          <t>1.5600</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.5700</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司</t>
+          <t>莱克电气股份有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 44.03</t>
+          <t>D- 1.24</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2415,49 +2421,51 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V10" s="3"/>
+        <v>1.1</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
+          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2467,7 +2475,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司2026年度第二期中期票据</t>
+          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2477,12 +2485,12 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2027-03-28</t>
         </is>
       </c>
       <c r="AK10" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL10" s="3" t="inlineStr">
@@ -2507,27 +2515,27 @@
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>白色家电</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2560,7 +2568,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26九合财金MTN001</t>
+          <t>26涪陵实业MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2570,64 +2578,62 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102690056.IB</t>
+          <t>DY102683843.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>78.98</v>
+        <v>94.58</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>25九合财金MTN003</t>
+          <t>26涪陵实业MTN001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>3.91Y</t>
+          <t>6.72Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.0800</t>
+          <t>2.1488</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/2.0500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C 25.55</t>
+          <t>C- 22.61</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2637,7 +2643,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2650,18 +2656,16 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U11" s="4" t="n">
-        <v>3.7</v>
-      </c>
+      <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2672,17 +2676,17 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2703,7 +2707,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2713,7 +2717,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2033-09-29</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2739,7 +2743,7 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
@@ -2787,12 +2791,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26四川港投MTN002</t>
+          <t>26温州现代MTN001</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2802,12 +2808,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683849.IB</t>
+          <t>102683848.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -2818,48 +2824,48 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>41.1</v>
+        <v>18.98</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25四川港投MTN001</t>
+          <t>24温州现代MTN001</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.30Y</t>
+          <t>110D+2.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7758</t>
+          <t>1.5117</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司</t>
+          <t>温州市现代服务业发展集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C 29.13</t>
+          <t>C+ 30.13</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2869,12 +2875,12 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2883,19 +2889,19 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.8</v>
+        <v>3.32</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2906,17 +2912,17 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
+          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2937,7 +2943,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2947,64 +2953,60 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
           <t>2029-09-29</t>
         </is>
       </c>
-      <c r="AK12" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AM12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3012,7 +3014,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3025,14 +3027,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26晋中公用MTN003</t>
+          <t>26天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3042,64 +3042,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683857.IB</t>
+          <t>102683840.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>2.50 ~ 3.00</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>43.1</v>
+        <v>129.17</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26晋中01</t>
+          <t>25天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.82Y+2.00Y</t>
+          <t>3.86Y+3.00Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7164</t>
+          <t>2.3549</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
+          <t>天津创业投资有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.23</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3123,17 +3123,19 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>1.1</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3141,20 +3143,24 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z13" s="3"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>山西省-晋中市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
+          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3175,7 +3181,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
+          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3185,14 +3191,10 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2034-09-29</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -3210,37 +3212,33 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP13" s="3"/>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR13" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3250,7 +3248,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3264,13 +3262,13 @@
         </is>
       </c>
       <c r="AZ13" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN003(科创债)</t>
+          <t>26余杭城投PPN003</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3280,27 +3278,31 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683851.IB</t>
+          <t>032680543.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>29.98</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -3308,17 +3310,17 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN002(科创债)</t>
+          <t>26余杭城投PPN002</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+N</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7277</t>
+          <t>1.7160</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3328,12 +3330,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
+          <t>杭州余杭城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 41.55</t>
+          <t>C 28.79</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3348,7 +3350,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3357,17 +3359,19 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V14" s="3"/>
+        <v>3.67</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3375,30 +3379,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
+          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
+          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3413,74 +3413,70 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
+          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
           <t>2029-09-29</t>
         </is>
       </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3488,12 +3484,12 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY14" s="3" t="inlineStr">
@@ -3506,74 +3502,66 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN005</t>
+          <t>26星乙V1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683842.IB</t>
+          <t>520508.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.0</v>
+        <v>1.5</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>39.1</v>
+        <v>83.98</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>26凤城河MTN004</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>2.99Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7018</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.6950/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>江油星乙农业投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 19.69</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3583,12 +3571,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3597,21 +3585,15 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="V15" s="4" t="n">
-        <v>1.25</v>
-      </c>
+        <v>2.36</v>
+      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X15" s="3"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3620,23 +3602,27 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3646,32 +3632,28 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3686,32 +3668,28 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3721,7 +3699,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3739,81 +3717,71 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN006</t>
+          <t>26星乙V2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683856.IB</t>
+          <t>520509.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.0</v>
+        <v>1.2</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.0</v>
+        <v>1.2</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 1.85</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>35.1</v>
+        <v>70.98</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>24越秀集团MTN007(绿色)</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.7050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>江油星乙农业投资集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.56</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3823,12 +3791,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3837,46 +3805,44 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.1</v>
-      </c>
+        <v>3.575</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X16" s="3"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3886,32 +3852,28 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
@@ -3929,11 +3891,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -3941,17 +3899,17 @@
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3961,7 +3919,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3984,59 +3942,59 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26温州现代MTN001</t>
+          <t>26鄂州01</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683848.IB</t>
+          <t>284128.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.6</v>
+        <v>2.19</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>18.98</v>
+        <v>77.98</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24温州现代MTN001</t>
+          <t>24鄂州01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>110D+2.00Y</t>
+          <t>175D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5117</t>
+          <t>1.6991</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -4046,12 +4004,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司</t>
+          <t>鄂州市新航程基础设施建设有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.56</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4061,12 +4019,12 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4075,46 +4033,44 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>1.47</v>
-      </c>
+        <v>3.16</v>
+      </c>
+      <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>湖北省-鄂州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4124,17 +4080,17 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
+          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
@@ -4145,7 +4101,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
@@ -4160,37 +4116,37 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4200,7 +4156,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4218,74 +4174,74 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003B</t>
+          <t>26淮新03</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683844.IB</t>
+          <t>284161.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.75</v>
+        <v>13.7</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.25</v>
+        <v>13.7</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.45</v>
+        <v>1.63</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>77.1</v>
+        <v>35.84</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002B</t>
+          <t>26淮新02</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>9.97Y</t>
+          <t>1.85Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.4907</t>
+          <t>1.6449</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2.5500/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>淮安新城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 25.04</t>
+          <t>C- 21.17</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4295,12 +4251,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 16:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4308,9 +4264,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>2.62</v>
-      </c>
+      <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -4319,7 +4273,7 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.37%~2.47%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4330,23 +4284,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4356,28 +4310,28 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种二)</t>
+          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
@@ -4397,27 +4351,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4445,66 +4399,64 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN002</t>
+          <t>26缙资03</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683853.IB</t>
+          <t>284127.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>8.0</v>
+        <v>7.1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>8.0</v>
+        <v>7.1</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>23.98</v>
+        <v>47.1</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN001</t>
+          <t>26缙资02</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6057</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4514,12 +4466,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司</t>
+          <t>缙云县国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.28</t>
+          <t>C 25.77</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4529,12 +4481,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4543,46 +4495,48 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.02</v>
-      </c>
+        <v>3.6901</v>
+      </c>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3"/>
+          <t>浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
+        <is>
+          <t>缙云县国有资本运营有限公司</t>
+        </is>
+      </c>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4592,28 +4546,32 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
+          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4633,7 +4591,7 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4653,7 +4611,7 @@
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4663,7 +4621,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
@@ -4681,14 +4639,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP029</t>
+          <t>26南宁高新PPN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4698,64 +4654,64 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>012682366.IB</t>
+          <t>032680546.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
+        <v>4.5</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.0</v>
+        <v>4.5</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>1.90 ~ 2.30</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>39.03</v>
+        <v>56.98</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP025</t>
+          <t>26南高K1</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>4.63Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.9599</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>南宁高新产业建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B 51.36</t>
+          <t>D+ 7.29</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4770,7 +4726,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4779,19 +4735,19 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4802,12 +4758,12 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
+          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
@@ -4818,7 +4774,7 @@
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4833,17 +4789,17 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
+          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK20" s="3"/>
@@ -4864,32 +4820,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4918,13 +4874,13 @@
         </is>
       </c>
       <c r="AZ20" s="4" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN003</t>
+          <t>26洞庭实业PPN002</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4932,45 +4888,51 @@
           <t>09-28 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>032690027.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F21" s="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>29.98</v>
+        <v>95.98</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN002</t>
+          <t>26洞庭实业PPN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7160</t>
+          <t>2.1752</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4980,12 +4942,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司</t>
+          <t>湖南洞庭新实业集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 29.86</t>
+          <t>D+ 7.11</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5000,7 +4962,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -5009,40 +4971,38 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>湖南省-岳阳市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
+          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
@@ -5063,7 +5023,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5094,37 +5054,37 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
@@ -5134,7 +5094,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5152,53 +5112,45 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN002</t>
+          <t>满坤转债</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C22" s="3"/>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>123287.SZ</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>2.00 ~ 2.80</t>
-        </is>
-      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="4" t="n">
-        <v>2.37</v>
+        <v>0.2</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>95.98</v>
+        <v>-125.9</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>26洞庭实业PPN001</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>4.75Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.1752</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5208,14 +5160,10 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>D+ 7.53</t>
-        </is>
-      </c>
+          <t>吉安满坤科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P22" s="3"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5223,7 +5171,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 09:15</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5233,7 +5181,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U22" s="3"/>
@@ -5243,107 +5191,103 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>2.15%~2.25%</t>
-        </is>
-      </c>
+      <c r="X22" s="3"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z22" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>湖南省-岳阳市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
+          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2032-09-28</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="AP22" s="3"/>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5376,53 +5320,45 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26南宁高新PPN002</t>
+          <t>常青转债</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
-        </is>
-      </c>
-      <c r="C23" s="3"/>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>113711.SH</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.5</v>
+        <v>8.0</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.30</t>
-        </is>
-      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="4" t="n">
-        <v>1.98</v>
+        <v>0.2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>56.98</v>
+        <v>-125.9</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>26南高K1</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>4.63Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.9599</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5432,14 +5368,10 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>D+ 7.69</t>
-        </is>
-      </c>
+          <t>江苏常青树新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5447,131 +5379,123 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 09:30</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>1.06</v>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>2.11%~2.21%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X23" s="3"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z23" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
+          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2032-09-28</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP23" s="3"/>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5599,66 +5523,62 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ23" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ23" s="3"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26天津创投MTN001(科创债)</t>
+          <t>26科集01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683840.IB</t>
+          <t>520510.SZ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.00</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.85</v>
+        <v>2.04</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>129.17</v>
+        <v>62.98</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25天津创投MTN001(科创债)</t>
+          <t>23创集K2</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>3.86Y+3.00Y</t>
+          <t>85D+2.00Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>1.5161</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5668,12 +5588,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司</t>
+          <t>惠州大亚湾科创集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>D- 1.80</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5683,33 +5603,29 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5717,30 +5633,26 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
+          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5750,28 +5662,28 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
+          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2034-09-29</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5781,38 +5693,42 @@
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP24" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV24" s="3" t="inlineStr">
@@ -5822,7 +5738,7 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
@@ -5835,14 +5751,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26缙资03</t>
+          <t>26龙翔01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5852,7 +5766,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>284127.SH</t>
+          <t>520506.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5861,38 +5775,38 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>7.1</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>2.20 ~ 2.90</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>47.1</v>
+        <v>91.1</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26缙资02</t>
+          <t>25射阳02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>3.39Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.7968</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5902,12 +5816,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司</t>
+          <t>龙翔投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.52</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5927,45 +5841,45 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.28%~2.38%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资本运营有限公司</t>
+          <t>长春新区发展集团有限公司</t>
         </is>
       </c>
       <c r="AE25" s="3" t="inlineStr">
@@ -5980,12 +5894,12 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5995,12 +5909,12 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="AK25" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休8</t>
         </is>
       </c>
       <c r="AL25" s="3" t="inlineStr">
@@ -6015,37 +5929,37 @@
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>生物制品</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6078,72 +5992,74 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26淮新03</t>
+          <t>26常德城发MTN002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284161.SH</t>
+          <t>102683854.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>35.84</v>
+        <v>35.98</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26淮新02</t>
+          <t>24常发01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1.85Y</t>
+          <t>2.73Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6449</t>
+          <t>1.7117</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>1.7300/1.7100</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司</t>
+          <t>常德市城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 23.26</t>
+          <t>C+ 33.57</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6153,12 +6069,12 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-28 16:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6166,8 +6082,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -6175,34 +6095,34 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
+          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
+          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6212,75 +6132,75 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6301,77 +6221,81 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26乐城02</t>
+          <t>26九合财金MTN001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>284142.SH</t>
+          <t>102690056.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>44.1</v>
+        <v>78.98</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26乐城01</t>
+          <t>25九合财金MTN003</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>2.82Y</t>
+          <t>3.91Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7085</t>
+          <t>2.0800</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.7400/1.6900</t>
+          <t>--/2.0500</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司</t>
+          <t>淄博市临淄区九合财金控股有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6381,7 +6305,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6391,19 +6315,21 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U27" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>3.74</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6414,23 +6340,23 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
+          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,平安证券股份有限公司</t>
+          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6440,32 +6366,28 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK27" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6475,37 +6397,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6538,72 +6460,74 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26鄂州01</t>
+          <t>26东航股MTN002</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284128.SH</t>
+          <t>102683841.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>24.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>24.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.19</v>
+        <v>1.53</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>77.98</v>
+        <v>24.1</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24鄂州01</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>175D</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6991</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>B 52.36</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6613,12 +6537,12 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -6626,121 +6550,127 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U28" s="3"/>
+      <c r="U28" s="4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
+          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>航空运输</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6761,77 +6691,81 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ28" s="3"/>
+      <c r="AZ28" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26滨江04</t>
+          <t>26杭州钢铁SCP003</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284047.SH</t>
+          <t>012682363.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>9.7</v>
-      </c>
-      <c r="F29" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>36.1</v>
+        <v>16.48</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24滨江投资PPN003</t>
+          <t>26杭州钢铁SCP002</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>200D</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6778</t>
+          <t>1.5172</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 18.94</t>
+          <t>C- 18.24</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6841,29 +6775,31 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U29" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>2.66</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6874,23 +6810,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
+          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6900,32 +6836,28 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6935,37 +6867,37 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6998,7 +6930,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP002</t>
+          <t>26厦门航空MTN002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -7008,49 +6940,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>012682332.IB</t>
+          <t>102683855.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>36.48</v>
+        <v>29.1</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP001(绿色)</t>
+          <t>26厦门航空MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5600</t>
+          <t>1.6600</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -7060,12 +6992,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司</t>
+          <t>厦门航空有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>B- 37.15</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7089,51 +7021,49 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.18</v>
+      </c>
+      <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
+          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -7143,7 +7073,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
+          <t>厦门航空有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7153,12 +7083,12 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-03-28</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK30" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL30" s="3" t="inlineStr">
@@ -7183,27 +7113,27 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>白色家电</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7236,58 +7166,76 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>满坤转债</t>
+          <t>26桂铁投MTN002</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>123287.SZ</t>
+          <t>102683852.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+        <v>11.0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="n">
-        <v>0.2</v>
+        <v>1.72</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-125.9</v>
+        <v>30.98</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>26桂铁07</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>2.95Y+2.00Y</t>
+        </is>
+      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7092</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>吉安满坤科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3"/>
+          <t>广西铁路投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.19</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7295,71 +7243,75 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:15</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>2.5273</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.75%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
+          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7369,54 +7321,58 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP31" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7426,7 +7382,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7439,63 +7395,83 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ31" s="3"/>
+      <c r="AZ31" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>常青转债</t>
+          <t>26四川港投MTN002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>113711.SH</t>
+          <t>102683849.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 1.90</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-125.9</v>
+        <v>41.1</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>25四川港投MTN001</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>3.30Y</t>
+        </is>
+      </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7758</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>江苏常青树新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P32" s="3"/>
+          <t>四川省港航投资集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>C 27.92</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7503,71 +7479,75 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:30</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
+          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
+          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7577,56 +7557,64 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP32" s="3"/>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7647,62 +7635,66 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26科集01</t>
+          <t>26鲁能源MTN003(科创债)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>520510.SZ</t>
+          <t>102683851.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>62.98</v>
+        <v>44.1</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>23创集K2</t>
+          <t>26鲁能源MTN002(科创债)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>85D+2.00Y</t>
+          <t>2.93Y+N</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5161</t>
+          <t>1.7277</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7712,12 +7704,12 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>D- 1.80</t>
+          <t>B- 39.23</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7727,56 +7719,62 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="U33" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z33" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
+          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司</t>
+          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7786,75 +7784,79 @@
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>房地产服务</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>其他房地产服务</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7862,12 +7864,12 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY33" s="3" t="inlineStr">
@@ -7880,17 +7882,17 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26星乙V1</t>
+          <t>26厦门市政MTN002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>520508.SZ</t>
+          <t>102683853.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7899,30 +7901,40 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>83.98</v>
+        <v>23.98</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>26厦门市政MTN001</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>2.51Y</t>
+        </is>
+      </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6057</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7932,10 +7944,14 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P34" s="3"/>
+          <t>厦门市政集团有限公司</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.86</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -7943,12 +7959,12 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7956,43 +7972,47 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>中合中小企业融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8002,17 +8022,17 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
@@ -8023,41 +8043,57 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP34" s="3"/>
-      <c r="AQ34" s="3"/>
-      <c r="AR34" s="3"/>
-      <c r="AS34" s="3"/>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8075,22 +8111,24 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26龙翔01</t>
+          <t>26凤城河MTN005</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>520506.SZ</t>
+          <t>102683842.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -8099,53 +8137,55 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.90</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>91.1</v>
+        <v>39.1</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25射阳02</t>
+          <t>26凤城河MTN004</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>3.39Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7968</t>
+          <t>1.7018</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6950/1.6900</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 20.08</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8155,29 +8195,33 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.28%~2.38%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8188,27 +8232,23 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
+          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3" t="inlineStr">
-        <is>
-          <t>长春新区发展集团有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8218,82 +8258,82 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK35" s="3" t="inlineStr">
         <is>
-          <t>休8</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>其他基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>生物制品</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
@@ -8311,67 +8351,83 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ35" s="3"/>
+      <c r="AZ35" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26星乙V2</t>
+          <t>26涪陵实业MTN003</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>520509.SZ</t>
+          <t>102683844.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>1.75</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>3.25</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>70.98</v>
+        <v>77.1</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>26涪陵实业MTN002B</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>9.97Y</t>
+        </is>
+      </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.4907</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.5500/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P36" s="3"/>
+          <t>重庆市涪陵实业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>C- 22.61</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -8379,12 +8435,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8392,14 +8448,20 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U36" s="3"/>
+      <c r="U36" s="4" t="n">
+        <v>2.62</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>2.37%~2.47%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8408,27 +8470,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD36" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8438,62 +8496,78 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO36" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP36" s="3"/>
-      <c r="AQ36" s="3"/>
-      <c r="AR36" s="3"/>
-      <c r="AS36" s="3"/>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW36" s="3" t="inlineStr">
@@ -8511,7 +8585,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ36" s="3"/>
+      <c r="AZ36" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
@@ -8573,7 +8649,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.7700</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -8583,7 +8659,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 14.99</t>
+          <t>C- 12.77</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8752,7 +8828,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26常德城发MTN002</t>
+          <t>26越秀集团MTN007</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8762,64 +8838,64 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102683854.IB</t>
+          <t>102683847.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.5</v>
+        <v>7.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2.5</v>
+        <v>7.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.55 ~ 1.85</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>35.98</v>
+        <v>35.1</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24常发01</t>
+          <t>24越秀集团MTN007(绿色)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.73Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7117</t>
+          <t>1.6850</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7050/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 38.58</t>
+          <t>B- 37.63</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8834,7 +8910,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8843,19 +8919,17 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1.4</v>
-      </c>
+        <v>1.8143</v>
+      </c>
+      <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
@@ -8866,17 +8940,17 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
+          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8897,7 +8971,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
+          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8907,10 +8981,14 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8928,32 +9006,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8981,14 +9059,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ38" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ38" s="3"/>
     </row>
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN007</t>
+          <t>26越秀集团MTN006</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8998,7 +9074,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102683847.IB</t>
+          <t>102683856.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9045,7 +9121,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7050/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -9055,7 +9131,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.56</t>
+          <t>B- 37.63</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9070,7 +9146,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -9079,9 +9155,11 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>1.8143</v>
-      </c>
-      <c r="V39" s="3"/>
+        <v>1.6857</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -9110,7 +9188,7 @@
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -9131,7 +9209,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
+          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>4.37</v>
+        <v>4.3667</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
@@ -2568,7 +2568,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003A(取消发行)</t>
+          <t>26温州现代MTN001</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2578,47 +2578,49 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>DY102683843.IB</t>
+          <t>102683848.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>94.58</v>
+        <v>18.98</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>24温州现代MTN001</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>6.72Y</t>
+          <t>110D+2.00Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.1488</t>
+          <t>1.5117</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2628,12 +2630,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>温州市现代服务业发展集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 22.61</t>
+          <t>C+ 30.13</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2643,12 +2645,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2656,37 +2658,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>1.47</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
@@ -2707,7 +2713,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
+          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2717,7 +2723,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2033-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2738,7 +2744,7 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
@@ -2753,22 +2759,22 @@
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV11" s="3" t="inlineStr">
@@ -2778,7 +2784,7 @@
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2791,14 +2797,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ11" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ11" s="3"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26温州现代MTN001</t>
+          <t>26天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2808,49 +2812,49 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683848.IB</t>
+          <t>102683840.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.50 ~ 3.00</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.6</v>
+        <v>2.85</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18.98</v>
+        <v>129.17</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24温州现代MTN001</t>
+          <t>25天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>110D+2.00Y</t>
+          <t>3.86Y+3.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.5117</t>
+          <t>2.3549</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2860,12 +2864,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司</t>
+          <t>天津创业投资有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.13</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2880,7 +2884,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2889,40 +2893,44 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.32</v>
+        <v>1.1</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.47</v>
+        <v>1.0</v>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z12" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
+          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2943,7 +2951,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
+          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2953,7 +2961,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2034-09-29</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2974,37 +2982,33 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP12" s="3"/>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>其他非银</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>产业集团</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>贸易</t>
-        </is>
-      </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
@@ -3027,12 +3031,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26天津创投MTN001(科创债)</t>
+          <t>26余杭城投PPN003</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3042,49 +3048,49 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683840.IB</t>
+          <t>032680543.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.00</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.85</v>
+        <v>1.71</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>129.17</v>
+        <v>29.98</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>25天津创投MTN001(科创债)</t>
+          <t>26余杭城投PPN002</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.86Y+3.00Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>1.7160</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3094,12 +3100,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司</t>
+          <t>杭州余杭城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 28.79</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3114,7 +3120,7 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3123,50 +3129,46 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.1</v>
+        <v>3.67</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>1.0</v>
+        <v>1.2</v>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
+          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3181,17 +3183,17 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
+          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2034-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3212,33 +3214,37 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP13" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3261,66 +3267,56 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ13" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ13" s="3"/>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN003</t>
+          <t>26星乙V1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>032680543.IB</t>
+          <t>520508.SZ</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>29.98</v>
+        <v>83.98</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>26余杭城投PPN002</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>2.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7160</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司</t>
+          <t>江油星乙农业投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 28.79</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3345,12 +3341,12 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -3359,46 +3355,44 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="V14" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>2.36</v>
+      </c>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>1.76%~1.86%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X14" s="3"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3408,12 +3402,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3429,7 +3423,7 @@
       <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
@@ -3444,47 +3438,43 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP14" s="3"/>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3502,7 +3492,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26星乙V1</t>
+          <t>26星乙V2</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3512,7 +3502,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520508.SZ</t>
+          <t>520509.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3521,10 +3511,10 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -3532,10 +3522,10 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>83.98</v>
+        <v>70.98</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -3585,7 +3575,7 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.36</v>
+        <v>3.575</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
@@ -3607,7 +3597,7 @@
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
@@ -3617,7 +3607,7 @@
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>中合中小企业融资担保股份有限公司</t>
+          <t>成都中小企业融资担保有限责任公司</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr">
@@ -3637,7 +3627,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3722,7 +3712,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26星乙V2</t>
+          <t>26鄂州01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3732,7 +3722,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>520509.SZ</t>
+          <t>284128.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3741,105 +3731,113 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.2</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.2</v>
+        <v>10.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>70.98</v>
+        <v>77.98</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>24鄂州01</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>175D</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>1.6991</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>鄂州市新航程基础设施建设有限公司</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>C- 15.00</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>09-28 15:00</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.575</v>
+        <v>3.16</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X16" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>2.25%~2.35%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>湖北省-鄂州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>成都中小企业融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3852,12 +3850,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
+          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3888,28 +3886,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3919,7 +3921,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3942,7 +3944,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26鄂州01</t>
+          <t>26淮新03</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3952,64 +3954,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>284128.SH</t>
+          <t>284161.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>13.7</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>13.7</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>77.98</v>
+        <v>35.84</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24鄂州01</t>
+          <t>26淮新02</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>175D</t>
+          <t>1.85Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6991</t>
+          <t>1.6449</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司</t>
+          <t>淮安新城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 15.00</t>
+          <t>C- 21.17</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4019,7 +4021,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 16:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4032,39 +4034,37 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U17" s="4" t="n">
-        <v>3.16</v>
-      </c>
+      <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
+          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26淮新03</t>
+          <t>26缙资03</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4184,64 +4184,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>284161.SH</t>
+          <t>284127.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>35.84</v>
+        <v>47.1</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26淮新02</t>
+          <t>26缙资02</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1.85Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6449</t>
+          <t>1.7922</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司</t>
+          <t>缙云县国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 21.17</t>
+          <t>C 25.77</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-28 16:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4264,40 +4264,46 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>3.6901</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3"/>
+          <t>浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr">
+        <is>
+          <t>缙云县国有资本运营有限公司</t>
+        </is>
+      </c>
       <c r="AE18" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4315,7 +4321,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4325,10 +4331,14 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4351,22 +4361,22 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
@@ -4381,7 +4391,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
@@ -4404,59 +4414,59 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26缙资03</t>
+          <t>26南宁高新PPN002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>284127.SH</t>
+          <t>032680546.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.90 ~ 2.30</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>47.1</v>
+        <v>56.98</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26缙资02</t>
+          <t>26南高K1</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>4.63Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.9599</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4466,12 +4476,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司</t>
+          <t>南宁高新产业建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C 25.77</t>
+          <t>D+ 7.29</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4481,12 +4491,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4495,48 +4505,46 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.6901</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>2.67</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
+          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD19" s="3" t="inlineStr">
-        <is>
-          <t>缙云县国有资本运营有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4546,12 +4554,12 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4561,67 +4569,63 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW19" s="3" t="inlineStr">
@@ -4639,12 +4643,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26南宁高新PPN002</t>
+          <t>26洞庭实业PPN002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4654,7 +4660,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>032680546.IB</t>
+          <t>032690027.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4663,40 +4669,40 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>56.98</v>
+        <v>95.98</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26南高K1</t>
+          <t>26洞庭实业PPN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.63Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.9599</t>
+          <t>2.1752</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4706,12 +4712,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司</t>
+          <t>湖南洞庭新实业集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.29</t>
+          <t>D+ 7.11</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4726,7 +4732,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4735,19 +4741,17 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V20" s="4" t="n">
-        <v>1.06</v>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4758,17 +4762,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>湖南省-岳阳市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
+          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4789,7 +4793,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4820,32 +4824,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4873,14 +4877,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN002</t>
+          <t>26杭州钢铁SCP003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4890,49 +4892,49 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>032690027.IB</t>
+          <t>012682363.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.5</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5</v>
+        <v>5.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.37</v>
+        <v>1.36</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>95.98</v>
+        <v>16.48</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN001</t>
+          <t>26杭州钢铁SCP002</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>200D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2.1752</t>
+          <t>1.5172</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4942,12 +4944,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.11</t>
+          <t>C- 18.24</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4957,12 +4959,12 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4971,44 +4973,44 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.44</v>
+        <v>2.66</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>湖南省-岳阳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
+          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司</t>
+          <t>杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5023,17 +5025,17 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-03-26</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -5059,27 +5061,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5112,130 +5114,142 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>满坤转债</t>
+          <t>26涪陵实业MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>123287.SZ</t>
+          <t>DY102683843.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>-125.9</v>
-      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>26涪陵实业MTN001</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>6.72Y</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>2.1488</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>重庆市涪陵实业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>C- 22.61</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>09-28 14:00</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>吉安满坤科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:15</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X22" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>2.17%~2.27%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5245,56 +5259,60 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2033-09-29</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO22" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP22" s="3"/>
-      <c r="AQ22" s="3" t="inlineStr">
-        <is>
-          <t>电子制造</t>
-        </is>
-      </c>
-      <c r="AR22" s="3" t="inlineStr">
-        <is>
-          <t>电子元器件</t>
-        </is>
-      </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>电子元器件</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>元件</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5315,50 +5333,66 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>常青转债</t>
+          <t>26涪陵实业MTN003</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>113711.SH</t>
+          <t>102683844.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+        <v>1.75</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 3.00</t>
+        </is>
+      </c>
       <c r="H23" s="4" t="n">
-        <v>0.2</v>
+        <v>2.45</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-125.9</v>
+        <v>77.1</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>26涪陵实业MTN002B</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>9.97Y</t>
+        </is>
+      </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.4907</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5368,10 +5402,14 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>江苏常青树新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3"/>
+          <t>重庆市涪陵实业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>C- 22.61</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5379,71 +5417,73 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:30</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U23" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>2.62</v>
+      </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X23" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>2.37%~2.47%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5453,56 +5493,60 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO23" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP23" s="3"/>
-      <c r="AQ23" s="3" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5523,62 +5567,66 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ23" s="3"/>
+      <c r="AZ23" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26科集01</t>
+          <t>26鲁能源MTN003(科创债)</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>520510.SZ</t>
+          <t>102683851.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F24" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>62.98</v>
+        <v>44.1</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>23创集K2</t>
+          <t>26鲁能源MTN002(科创债)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>85D+2.00Y</t>
+          <t>2.93Y+N</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.5161</t>
+          <t>1.7277</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5588,12 +5636,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>D- 1.80</t>
+          <t>B- 39.23</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5603,56 +5651,62 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="U24" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>3.915</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z24" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
+          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司</t>
+          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5662,75 +5716,79 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO24" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ24" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR24" s="3" t="inlineStr">
-        <is>
-          <t>房地产服务</t>
-        </is>
-      </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>其他房地产服务</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>房地产开发</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5738,12 +5796,12 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY24" s="3" t="inlineStr">
@@ -5756,57 +5814,45 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26龙翔01</t>
+          <t>满坤转债</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>520506.SZ</t>
+          <t>123287.SZ</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.0</v>
+        <v>7.6</v>
       </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>2.20 ~ 2.90</t>
-        </is>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="4" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>91.1</v>
+        <v>-125.9</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>25射阳02</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>3.39Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7968</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5816,14 +5862,10 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
+          <t>吉安满坤科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5831,7 +5873,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:15</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5841,55 +5883,51 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>2.28%~2.38%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X25" s="3"/>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z25" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
+          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>长春新区发展集团有限公司</t>
-        </is>
-      </c>
+          <t>平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5899,24 +5937,20 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2032-09-28</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5924,7 +5958,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -5934,32 +5968,28 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP25" s="3"/>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>生物制品</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5969,7 +5999,7 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -5992,76 +6022,58 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26常德城发MTN002</t>
+          <t>常青转债</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683854.IB</t>
+          <t>113711.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
       <c r="H26" s="4" t="n">
-        <v>1.77</v>
+        <v>0.2</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>35.98</v>
+        <v>-125.9</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>24常发01</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>2.73Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7117</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.57</t>
-        </is>
-      </c>
+          <t>江苏常青树新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -6069,75 +6081,71 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 09:30</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>1.4</v>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t>1.67%~1.77%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X26" s="3"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z26" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
+          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
+          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6147,53 +6155,49 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2032-09-28</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP26" s="3"/>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6221,24 +6225,22 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ26" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ26" s="3"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26九合财金MTN001</t>
+          <t>26科集01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102690056.IB</t>
+          <t>520510.SZ</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -6247,55 +6249,53 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>78.98</v>
+        <v>62.98</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>25九合财金MTN003</t>
+          <t>23创集K2</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.91Y</t>
+          <t>85D+2.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.0800</t>
+          <t>1.5161</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/2.0500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司</t>
+          <t>惠州大亚湾科创集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 22.25</t>
+          <t>D- 1.80</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6315,16 +6315,14 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>3.74</v>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
@@ -6340,23 +6338,23 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
+          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6366,28 +6364,28 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
+          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6397,37 +6395,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6460,17 +6458,17 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN002</t>
+          <t>26龙翔01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>102683841.IB</t>
+          <t>520506.SZ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6479,55 +6477,53 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>24.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>2.20 ~ 2.90</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>24.1</v>
+        <v>91.1</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>25射阳02</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>3.39Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7968</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>龙翔投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B 52.36</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6537,133 +6533,135 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>1.7</v>
-      </c>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>2.28%~2.38%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3"/>
+          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
+        <is>
+          <t>长春新区发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
+          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休8</t>
         </is>
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>生物制品</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6673,7 +6671,7 @@
       </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6691,14 +6689,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ28" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ28" s="3"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP003</t>
+          <t>26常德城发MTN002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6708,64 +6704,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>012682363.IB</t>
+          <t>102683854.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.48</v>
+        <v>35.98</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP002</t>
+          <t>24常发01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>2.73Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.5172</t>
+          <t>1.7117</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>1.7300/1.7100</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>常德市城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C- 18.24</t>
+          <t>C+ 33.57</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6775,12 +6771,12 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -6789,17 +6785,19 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="V29" s="3"/>
+        <v>2.92</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6810,23 +6808,23 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
+          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6841,7 +6839,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6851,7 +6849,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6872,32 +6870,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6925,12 +6923,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ29" s="3"/>
+      <c r="AZ29" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN002</t>
+          <t>26九合财金MTN001</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6940,64 +6940,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102683855.IB</t>
+          <t>102690056.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>29.1</v>
+        <v>78.98</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN001(可持续挂钩)</t>
+          <t>25九合财金MTN003</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>3.91Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6600</t>
+          <t>2.0800</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0500</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司</t>
+          <t>淄博市临淄区九合财金控股有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 37.15</t>
+          <t>C- 22.25</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7021,38 +7021,38 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.18</v>
+        <v>3.74</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
+          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司2026年度第二期中期票据</t>
+          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7083,14 +7083,10 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -7108,32 +7104,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7166,7 +7162,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26桂铁投MTN002</t>
+          <t>26东航股MTN002</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7176,64 +7172,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102683852.IB</t>
+          <t>102683841.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.0</v>
+        <v>24.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>11.0</v>
+        <v>24.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>30.98</v>
+        <v>24.1</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26桂铁07</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+2.00Y</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7092</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.19</t>
+          <t>B 52.36</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7243,12 +7239,12 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -7257,19 +7253,17 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.5273</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>32.0</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7280,17 +7274,17 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
+          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7301,7 +7295,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7311,7 +7305,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
+          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7321,10 +7315,14 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -7342,37 +7340,37 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7382,7 +7380,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7396,13 +7394,13 @@
         </is>
       </c>
       <c r="AZ31" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26四川港投MTN002</t>
+          <t>26厦门航空MTN002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7412,7 +7410,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683849.IB</t>
+          <t>102683855.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -7421,55 +7419,55 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>41.1</v>
+        <v>29.1</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25四川港投MTN001</t>
+          <t>26厦门航空MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>3.30Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.7758</t>
+          <t>1.6600</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司</t>
+          <t>厦门航空有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C 27.92</t>
+          <t>B- 37.15</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7479,12 +7477,12 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -7493,19 +7491,17 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>2.18</v>
+      </c>
+      <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7516,17 +7512,17 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
+          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7537,7 +7533,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7547,7 +7543,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>厦门航空有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7582,32 +7578,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7635,14 +7631,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN003(科创债)</t>
+          <t>26桂铁投MTN002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7652,19 +7646,19 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683851.IB</t>
+          <t>102683852.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -7672,44 +7666,44 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>44.1</v>
+        <v>30.98</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN002(科创债)</t>
+          <t>26桂铁07</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.93Y+N</t>
+          <t>2.95Y+2.00Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7277</t>
+          <t>1.7092</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
+          <t>广西铁路投资集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 39.23</t>
+          <t>C+ 33.19</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7733,17 +7727,19 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V33" s="3"/>
+        <v>2.5273</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7751,24 +7747,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
+          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7789,7 +7781,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
+          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7799,64 +7791,60 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t>2029-09-29</t>
         </is>
       </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
-      <c r="AL33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7864,12 +7852,12 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY33" s="3" t="inlineStr">
@@ -7877,12 +7865,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN002</t>
+          <t>26四川港投MTN002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7892,64 +7882,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683853.IB</t>
+          <t>102683849.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23.98</v>
+        <v>41.1</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN001</t>
+          <t>25四川港投MTN001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>3.30Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.6057</t>
+          <t>1.7758</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司</t>
+          <t>四川省港航投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 24.86</t>
+          <t>C 27.92</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7964,7 +7954,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7973,19 +7963,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.0</v>
+        <v>4.8</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7996,17 +7986,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
+          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -8027,7 +8017,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
+          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8037,10 +8027,14 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8063,7 +8057,7 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -8073,12 +8067,12 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -8118,7 +8112,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN005</t>
+          <t>26厦门市政MTN002</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8128,121 +8122,121 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683842.IB</t>
+          <t>102683853.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>26厦门市政MTN001</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2.51Y</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1.6057</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>厦门市政集团有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.86</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>09-28 11:00</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F35" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>26凤城河MTN004</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>2.99Y</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>1.7018</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>1.6950/1.6900</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>泰州凤城河建设发展有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>C- 20.08</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>09-28 10:00</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>3.83</v>
-      </c>
       <c r="V35" s="4" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
+          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8263,7 +8257,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
+          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8273,14 +8267,10 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8303,27 +8293,27 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8352,13 +8342,13 @@
         </is>
       </c>
       <c r="AZ35" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003</t>
+          <t>26凤城河MTN005</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8368,64 +8358,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683844.IB</t>
+          <t>102683842.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1.75</v>
+        <v>3.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3.25</v>
+        <v>3.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.00</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>77.1</v>
+        <v>39.1</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN002B</t>
+          <t>26凤城河MTN004</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>9.97Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.4907</t>
+          <t>1.7018</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>2.5500/--</t>
+          <t>1.6950/1.6900</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 22.61</t>
+          <t>C- 20.08</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8435,12 +8425,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8449,17 +8439,19 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V36" s="3"/>
+        <v>3.8333</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>2.37%~2.47%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8470,17 +8462,17 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8501,7 +8493,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据</t>
+          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8511,10 +8503,14 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8542,22 +8538,22 @@
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-30" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-01" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C 28.12</t>
+          <t>C 28.41</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.03</t>
+          <t>B- 36.81</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.44</t>
+          <t>C+ 31.83</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26晋中公用MTN003</t>
+          <t>26夏商SCP029</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1402,64 +1402,64 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683857.IB</t>
+          <t>012682366.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.12Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.30 ~ 1.51</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>43.1</v>
+        <v>39.03</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26晋中01</t>
+          <t>26夏商SCP025</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.82Y+2.00Y</t>
+          <t>53D</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.7164</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.98</t>
+          <t>B- 49.82</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1483,17 +1483,19 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V6" s="3"/>
+        <v>2.8</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1504,23 +1506,23 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>山西省-晋中市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
+          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1535,7 +1537,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1545,14 +1547,10 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2026-11-13</t>
+        </is>
+      </c>
+      <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1570,32 +1568,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1624,13 +1622,13 @@
         </is>
       </c>
       <c r="AZ6" s="4" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP029</t>
+          <t>26莱克电气SCP002</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1640,12 +1638,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>012682366.IB</t>
+          <t>012682332.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.12Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1656,48 +1654,48 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.51</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>39.03</v>
+        <v>36.48</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP025</t>
+          <t>26莱克电气SCP001(绿色)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>53D</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.5600</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/1.5700</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>莱克电气股份有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 49.42</t>
+          <t>D- 3.00</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1712,7 +1710,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1721,40 +1719,40 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，拟全部用于偿还发行人本部银行借款。</t>
+          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1765,7 +1763,7 @@
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
@@ -1775,7 +1773,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十九期超短期融资券</t>
+          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1785,10 +1783,14 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="AK7" s="3"/>
+          <t>2027-03-28</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -1811,27 +1813,27 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>其他设备制造</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>综合设备制造</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>白色家电</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1859,79 +1861,79 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26乐城02</t>
+          <t>26温州现代MTN001</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>284142.SH</t>
+          <t>102683848.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>44.1</v>
+        <v>18.98</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26乐城01</t>
+          <t>24温州现代MTN001</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.82Y</t>
+          <t>110D+2.00Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7085</t>
+          <t>1.5117</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.7400/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司</t>
+          <t>温州市现代服务业发展集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>B- 37.18</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1941,34 +1943,38 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.47</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
@@ -1979,18 +1985,18 @@
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
+          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,平安证券股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -2000,32 +2006,28 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -2035,12 +2037,12 @@
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
@@ -2050,27 +2052,27 @@
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV8" s="3" t="inlineStr">
@@ -2080,7 +2082,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2098,57 +2100,59 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26滨江04</t>
+          <t>26天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>284047.SH</t>
+          <t>102683840.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+3</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.7</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>2.50 ~ 3.00</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.65</v>
+        <v>2.85</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>36.1</v>
+        <v>129.17</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>24滨江投资PPN003</t>
+          <t>25天津创投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>3.86Y+3.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6778</t>
+          <t>2.3549</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2158,12 +2162,12 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司</t>
+          <t>天津创业投资有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 18.75</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2173,56 +2177,64 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z9" s="3"/>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
+          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2232,32 +2244,28 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2034-09-29</t>
+        </is>
+      </c>
+      <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM9" s="3" t="inlineStr">
@@ -2267,42 +2275,38 @@
       </c>
       <c r="AN9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP9" s="3"/>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV9" s="3" t="inlineStr">
@@ -2312,7 +2316,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2325,12 +2329,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP002</t>
+          <t>26余杭城投PPN003</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2340,64 +2346,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>012682332.IB</t>
+          <t>032680543.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>36.48</v>
+        <v>29.98</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26莱克电气SCP001(绿色)</t>
+          <t>26余杭城投PPN002</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5600</t>
+          <t>1.7160</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/1.5700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司</t>
+          <t>杭州余杭城市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>D- 1.24</t>
+          <t>C+ 30.44</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2412,7 +2418,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2421,51 +2427,51 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.1</v>
+        <v>3.67</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.0</v>
+        <v>1.2</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本次超短期融资券发行规模5亿元,拟全部用于偿还发行人有息负债或补充流动性资金。</t>
+          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司,中国民生银行股份有限公司,上海银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2475,24 +2481,20 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>莱克电气股份有限公司2026年度第二期超短期融资券</t>
+          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-03-28</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -2510,7 +2512,7 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
@@ -2520,27 +2522,27 @@
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>综合设备制造</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>白色家电</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV10" s="3" t="inlineStr">
@@ -2550,7 +2552,7 @@
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2568,59 +2570,51 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26温州现代MTN001</t>
+          <t>26星乙V1</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>102683848.IB</t>
+          <t>520508.SZ</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.0</v>
+        <v>1.5</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>18.98</v>
+        <v>83.98</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>24温州现代MTN001</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>110D+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5117</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2630,12 +2624,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司</t>
+          <t>江油星乙农业投资集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.13</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2645,12 +2639,12 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2659,46 +2653,44 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>1.47</v>
-      </c>
+        <v>2.36</v>
+      </c>
+      <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>1.59%~1.69%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X11" s="3"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期发行中期票据5亿元，拟全部用于偿还有息债务</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>中合中小企业融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2708,17 +2700,17 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>温州市现代服务业发展集团有限公司2026年度第一期中期票据</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
@@ -2729,7 +2721,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2747,11 +2739,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+      <c r="AP11" s="3"/>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -2759,32 +2747,32 @@
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2802,59 +2790,51 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26天津创投MTN001(科创债)</t>
+          <t>26星乙V2</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>102683840.IB</t>
+          <t>520509.SZ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5+3</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.0</v>
+        <v>1.2</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.0</v>
+        <v>1.2</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.00</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>129.17</v>
+        <v>70.98</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.65</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>25天津创投MTN001(科创债)</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>3.86Y+3.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.3549</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2864,7 +2844,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司</t>
+          <t>江油星乙农业投资集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
@@ -2879,12 +2859,12 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2893,50 +2873,44 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>3.575</v>
+      </c>
+      <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
           <t>8+</t>
         </is>
       </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>2.45%~2.55%</t>
-        </is>
-      </c>
+      <c r="X12" s="3"/>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>四川省-绵阳市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>拟用于科技创新领域的相关基金和股权直投项目的出资及偿还到期债务融资工具的利息</t>
+          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>成都中小企业融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
@@ -2946,28 +2920,28 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>天津创业投资有限公司2026年度第一期科技创新债券</t>
+          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2034-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
@@ -2982,23 +2956,23 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3"/>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
@@ -3008,17 +2982,17 @@
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3031,29 +3005,27 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN003</t>
+          <t>26鄂州01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>032680543.IB</t>
+          <t>284128.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -3064,33 +3036,33 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.71</v>
+        <v>2.19</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>29.98</v>
+        <v>77.98</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26余杭城投PPN002</t>
+          <t>24鄂州01</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>175D</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.7160</t>
+          <t>1.6991</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3100,12 +3072,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司</t>
+          <t>鄂州市新航程基础设施建设有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 28.79</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3115,12 +3087,12 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3129,46 +3101,44 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3.16</v>
+      </c>
+      <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.25%~2.35%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>湖北省-鄂州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期发行定向债务融资工具10.00亿元,期限3+2年。本期债券募集资金拟全部用于偿还有息负债,非政府一类债务,项目贷款均不涉及棚改及保障房。[23余杭城投PPN003]</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,浙商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3178,12 +3148,12 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭城市发展投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3199,7 +3169,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3214,12 +3184,12 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3229,12 +3199,12 @@
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
@@ -3244,7 +3214,7 @@
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3254,7 +3224,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3272,7 +3242,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26星乙V1</t>
+          <t>26淮新03</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3282,88 +3252,98 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>520508.SZ</t>
+          <t>284161.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.5</v>
+        <v>13.7</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.5</v>
+        <v>13.7</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>83.98</v>
+        <v>35.84</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>26淮新02</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>1.85Y</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>1.6449</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>1.7400/--</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>淮安新城投资开发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>C- 19.85</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>09-28 16:00</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>09-28 15:00</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U14" s="4" t="n">
-        <v>2.36</v>
-      </c>
+      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X14" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3372,24 +3352,20 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>中合中小企业融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3402,12 +3378,12 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种一)</t>
+          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3417,7 +3393,7 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3438,28 +3414,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3469,7 +3449,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3492,7 +3472,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26星乙V2</t>
+          <t>26缙资03</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3502,112 +3482,124 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520509.SZ</t>
+          <t>284127.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>70.98</v>
+        <v>47.1</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>26缙资02</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>2.75Y</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>1.7922</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>缙云县国有资产投资经营集团有限公司</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>C 25.77</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>09-28 15:00</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>江油星乙农业投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>09-28 15:00</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.575</v>
+        <v>3.6901</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X15" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>浙江省-丽水市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本次募集资金1.10亿元拟用于新建高标准粮仓及粮食仓储设A施升级改造建设项目建设,1.60亿元拟用于粮食仓储加工物流及配套设施设备建设项目建设</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>成都中小企业融资担保有限责任公司</t>
+          <t>缙云县国有资本运营有限公司</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr">
@@ -3622,12 +3614,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>江油星乙农业投资集团有限公司2026年面向专业投资者非公开发行乡村振兴公司债券(革命老区)(第一期)(品种二)</t>
+          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3637,13 +3629,17 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3658,10 +3654,14 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP15" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3712,17 +3712,17 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26鄂州01</t>
+          <t>26南宁高新PPN002</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>284128.SH</t>
+          <t>032680546.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3731,40 +3731,40 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>4.5</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>4.5</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.90 ~ 2.30</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>77.98</v>
+        <v>56.98</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>24鄂州01</t>
+          <t>26南高K1</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>175D</t>
+          <t>4.63Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6991</t>
+          <t>1.9599</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司</t>
+          <t>南宁高新产业建设开发集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 15.00</t>
+          <t>D+ 7.29</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3803,44 +3803,46 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="V16" s="3"/>
+        <v>2.67</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.25%~2.35%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>广西壮族自治区-南宁市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[24鄂州01,23鄂州02]</t>
+          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,天风证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3850,12 +3852,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>鄂州市新航程基础设施建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3871,54 +3873,54 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -3939,79 +3941,81 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26淮新03</t>
+          <t>26洞庭实业PPN002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>284161.SH</t>
+          <t>032690027.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>13.7</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>13.7</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>35.84</v>
+        <v>95.98</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26淮新02</t>
+          <t>26洞庭实业PPN001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.85Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6449</t>
+          <t>2.1752</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司</t>
+          <t>湖南洞庭新实业集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 21.17</t>
+          <t>D+ 7.11</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4021,7 +4025,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-28 16:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -4034,16 +4038,18 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>1.44</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4054,23 +4060,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>湖南省-岳阳市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币13.70亿元(含13.70亿元),发行人在扣除发行费用后,拟用于偿还到期公司债券本金[25淮新D2,25淮新Y1,24淮新01]</t>
+          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,南京证券股份有限公司</t>
+          <t>东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4080,12 +4086,12 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>淮安新城投资开发集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4095,13 +4101,13 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
@@ -4116,32 +4122,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4174,74 +4180,74 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26缙资03</t>
+          <t>26杭州钢铁SCP003</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>284127.SH</t>
+          <t>012682363.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>7.1</v>
+        <v>5.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7.1</v>
+        <v>5.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 1.70</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>47.1</v>
+        <v>16.48</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26缙资02</t>
+          <t>26杭州钢铁SCP002</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>200D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7922</t>
+          <t>1.5172</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司</t>
+          <t>杭州钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 25.77</t>
+          <t>C- 18.53</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4251,12 +4257,12 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4265,48 +4271,44 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.6901</v>
+        <v>2.66</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>浙江省-丽水市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将全部用于偿还到期的公司债券的本金。[24缙资01]</t>
+          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>缙云县国有资本运营有限公司</t>
-        </is>
-      </c>
+          <t>杭州银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4316,82 +4318,78 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>缙云县国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2027-03-26</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>普钢</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>钢铁</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW18" s="3" t="inlineStr">
@@ -4414,7 +4412,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26南宁高新PPN002</t>
+          <t>26涪陵实业MTN003A(取消发行)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4424,49 +4422,43 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>032680546.IB</t>
+          <t>DY102683843.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>4.5</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>56.98</v>
-      </c>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26南高K1</t>
+          <t>26涪陵实业MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.63Y</t>
+          <t>6.72Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.9599</t>
+          <t>2.1488</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4476,12 +4468,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.29</t>
+          <t>C 27.95</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4491,12 +4483,12 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
@@ -4504,20 +4496,16 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="U19" s="4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.06</v>
-      </c>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4528,23 +4516,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具,拟发行金额4.5亿元,期限5年,募集资金用于偿还即将到期的债务融资工具本金。[23南宁高新MTN002]</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4559,17 +4547,17 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>南宁高新产业建设开发集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2033-09-29</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4595,27 +4583,27 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4644,13 +4632,13 @@
         </is>
       </c>
       <c r="AZ19" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN002</t>
+          <t>26鲁能源MTN003(科创债)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4660,49 +4648,49 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>032690027.IB</t>
+          <t>102683851.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5</v>
+        <v>20.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5</v>
+        <v>20.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>95.98</v>
+        <v>44.1</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26洞庭实业PPN001</t>
+          <t>26鲁能源MTN002(科创债)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>2.93Y+N</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2.1752</t>
+          <t>1.7277</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4712,12 +4700,12 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司</t>
+          <t>山东能源集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.11</t>
+          <t>B- 37.08</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4732,7 +4720,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4741,44 +4729,48 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.44</v>
+        <v>3.915</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z20" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>湖南省-岳阳市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人计划本次基础发行金额为0元,发行金额上限0.50亿元的定向债务融资工具,拟全部用于偿还存量债务融资工具[23洞庭资源PPN001]</t>
+          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4793,20 +4785,24 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>湖南洞庭新实业集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -4829,27 +4825,27 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4864,12 +4860,12 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY20" s="3" t="inlineStr">
@@ -4882,7 +4878,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP003</t>
+          <t>26涪陵实业MTN003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4892,64 +4888,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682363.IB</t>
+          <t>102683844.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
+        <v>1.75</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.0</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.80 ~ 3.00</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>16.48</v>
+        <v>77.1</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26杭州钢铁SCP002</t>
+          <t>26涪陵实业MTN002B</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>9.97Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5172</t>
+          <t>2.4907</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.5500/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司</t>
+          <t>重庆市涪陵实业发展集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 18.24</t>
+          <t>C 27.95</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4959,12 +4955,12 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 14:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4973,44 +4969,44 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.66</v>
+        <v>2.6154</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.37%~2.47%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>重庆市-涪陵区</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金5亿元,用于偿还发行人有息债务本息</t>
+          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司</t>
+          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5025,7 +5021,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>杭州钢铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5035,7 +5031,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-26</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -5056,32 +5052,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>普钢</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5109,73 +5105,81 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ21" s="3"/>
+      <c r="AZ21" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003A(取消发行)</t>
+          <t>26乐城02</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>DY102683843.IB</t>
+          <t>284142.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>44.1</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN001</t>
+          <t>26乐城01</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>6.72Y</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2.1488</t>
+          <t>1.7085</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6900</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
+          <t>乐清市城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 22.61</t>
+          <t>C- 15.56</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5185,7 +5189,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5195,19 +5199,21 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U22" s="3"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>3.01</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5218,23 +5224,23 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还回售公司债券本金[23乐城02]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>国信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
@@ -5244,43 +5250,47 @@
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据(品种一)(取消发行)</t>
+          <t>乐清市城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2033-09-29</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
@@ -5290,22 +5300,22 @@
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5333,66 +5343,50 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26涪陵实业MTN003</t>
+          <t>满坤转债</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683844.IB</t>
+          <t>123287.SZ</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>1.80 ~ 3.00</t>
-        </is>
-      </c>
+        <v>7.6</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="4" t="n">
-        <v>2.45</v>
+        <v>0.2</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>77.1</v>
+        <v>-125.9</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>26涪陵实业MTN002B</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>9.97Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.4907</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5402,14 +5396,10 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>C- 22.61</t>
-        </is>
-      </c>
+          <t>吉安满坤科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5417,73 +5407,71 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-28 14:00</t>
+          <t>09-28 09:15</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>2.62</v>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>2.37%~2.47%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X23" s="3"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z23" s="3"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>重庆市-涪陵区</t>
+          <t>江西省-吉安市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额为0亿元,发行规模上限为3.25亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵实业PPN001]</t>
+          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>重庆市涪陵实业发展集团有限公司2026年度第三期中期票据</t>
+          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5493,53 +5481,49 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
+          <t>2032-09-28</t>
         </is>
       </c>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP23" s="3"/>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5567,66 +5551,50 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ23" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ23" s="3"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26鲁能源MTN003(科创债)</t>
+          <t>常青转债</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683851.IB</t>
+          <t>113711.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
+        <v>8.0</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="4" t="n">
-        <v>1.73</v>
+        <v>0.2</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>44.1</v>
+        <v>-125.9</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>26鲁能源MTN002(科创债)</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>2.93Y+N</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7277</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5636,14 +5604,10 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>B- 39.23</t>
-        </is>
-      </c>
+          <t>江苏常青树新材料科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P24" s="3"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -5651,77 +5615,71 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 09:30</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="n">
-        <v>3.915</v>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>1.67%~1.77%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X24" s="3"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额20亿元,本期中期票据募集资金全部用于偿还发行人本部有息债务[21山能债04,26鲁能源SCP001]</t>
+          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司</t>
+          <t>光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>山东能源集团有限公司2026年度第三期科技创新债券</t>
+          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5731,57 +5689,49 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2032-09-28</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP24" s="3"/>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5796,12 +5746,12 @@
       </c>
       <c r="AW24" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX24" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY24" s="3" t="inlineStr">
@@ -5814,120 +5764,136 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>满坤转债</t>
+          <t>26科集01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>09-28 19:00</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>520510.SZ</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>23创集K2</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>85D+2.00Y</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>1.5161</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>惠州大亚湾科创集团有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
           <t>09-28 15:00</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>123287.SZ</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>6Y</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>-125.9</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="S25" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>吉安满坤科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>09-28 09:15</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X25" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江西省-吉安市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本次发行可转换公司债券的募集资金总额不超过人民币76000.00万元(含76000.00万元),扣除发行费用后的募集资金净额拟用于投入泰国高端印制电路板生产基地项目和智能化与数字化升级改造项目</t>
+          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>平安证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5937,17 +5903,17 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>2026年吉安满坤科技股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK25" s="3"/>
@@ -5958,12 +5924,12 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
@@ -5971,25 +5937,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP25" s="3"/>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6022,58 +5992,76 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>常青转债</t>
+          <t>26常德城发MTN002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>113711.SH</t>
+          <t>102683854.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+        <v>2.5</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
       <c r="H26" s="4" t="n">
-        <v>0.2</v>
+        <v>1.77</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-125.9</v>
+        <v>35.98</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>24常发01</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>2.73Y</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7117</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/1.7100</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏常青树新材料科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3"/>
+          <t>常德市城市发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.71</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -6081,71 +6069,75 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:30</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X26" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本次向不特定对象发行可转换公司债券的募集资金总额不超过80,000.00万元,扣除发行费用后拟全部投入泰州高分子新材料生产基地(一期)项目</t>
+          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司</t>
+          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>2026年江苏常青树新材料科技股份有限公司公开发行可转换公司债券</t>
+          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6155,56 +6147,60 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2032-09-28</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP26" s="3"/>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>化学制品</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6225,22 +6221,24 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26科集01</t>
+          <t>26九合财金MTN001</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>520510.SZ</t>
+          <t>102690056.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -6249,53 +6247,55 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F27" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>2.20 ~ 3.20</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>62.98</v>
+        <v>78.98</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>23创集K2</t>
+          <t>25九合财金MTN003</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>85D+2.00Y</t>
+          <t>3.91Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.5161</t>
+          <t>2.0800</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.0500</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司</t>
+          <t>淄博市临淄区九合财金控股有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>D- 1.80</t>
+          <t>C 27.35</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6315,14 +6315,16 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="U27" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>3.74</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
@@ -6338,23 +6340,23 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金3亿元拟用于支付“23创集K1”因投资者回售而产生的本金[23创集K1]</t>
+          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司</t>
+          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6364,28 +6366,28 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>惠州大亚湾科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
@@ -6395,37 +6397,37 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>房地产服务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他房地产服务</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6458,17 +6460,17 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26龙翔01</t>
+          <t>26东航股MTN002</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-28 19:00</t>
+          <t>09-28 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>520506.SZ</t>
+          <t>102683841.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6477,53 +6479,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>24.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>24.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 2.90</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>91.1</v>
+        <v>24.1</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25射阳02</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>3.39Y</t>
+          <t>2.19Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.7968</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 46.50</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6533,145 +6537,143 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-28 15:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U28" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>1.7833</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.28%~2.38%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
+          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD28" s="3" t="inlineStr">
-        <is>
-          <t>长春新区发展集团有限公司</t>
-        </is>
-      </c>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK28" s="3" t="inlineStr">
         <is>
-          <t>休8</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>航空运输</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO28" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ28" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR28" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>生物制品</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW28" s="3" t="inlineStr">
@@ -6689,12 +6691,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ28" s="3"/>
+      <c r="AZ28" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26常德城发MTN002</t>
+          <t>26厦门航空MTN002</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6704,64 +6708,64 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>102683854.IB</t>
+          <t>102683855.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.5</v>
+        <v>6.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.5</v>
+        <v>6.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>35.98</v>
+        <v>29.1</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24常发01</t>
+          <t>26厦门航空MTN001(可持续挂钩)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.73Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7117</t>
+          <t>1.6600</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司</t>
+          <t>厦门航空有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.57</t>
+          <t>B- 37.87</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6776,7 +6780,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -6785,19 +6789,17 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V29" s="4" t="n">
-        <v>1.4</v>
-      </c>
+        <v>2.1833</v>
+      </c>
+      <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6808,17 +6810,17 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,募集资金拟全部用于即将到期的债务融资工具本金。[23常德城发PPN001]</t>
+          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,财信证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6829,7 +6831,7 @@
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6839,7 +6841,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>常德市城市发展集团有限公司2026年度第二期中期票据</t>
+          <t>厦门航空有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6849,10 +6851,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -6870,32 +6876,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6923,14 +6929,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ29" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ29" s="3"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26九合财金MTN001</t>
+          <t>26桂铁投MTN002</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6940,64 +6944,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>102690056.IB</t>
+          <t>102683852.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.20</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>78.98</v>
+        <v>30.98</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>25九合财金MTN003</t>
+          <t>26桂铁07</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>3.91Y</t>
+          <t>2.95Y+2.00Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.0800</t>
+          <t>1.7092</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/2.0500</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司</t>
+          <t>广西铁路投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 22.25</t>
+          <t>B- 36.12</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7012,7 +7016,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
@@ -7021,38 +7025,40 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="V30" s="3"/>
+        <v>2.5273</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>32.0</v>
+      </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模人民币0.00亿元,发行金额上限人民币10.00亿元,募集资金将全部用于偿还即将到期或回售的债务融资工具本金[23九合财金MTN001]</t>
+          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,青岛银行股份有限公司</t>
+          <t>中国银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7073,7 +7079,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>淄博市临淄区九合财金控股有限公司2026年度第一期中期票据</t>
+          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7109,32 +7115,32 @@
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV30" s="3" t="inlineStr">
@@ -7144,7 +7150,7 @@
       </c>
       <c r="AW30" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX30" s="3" t="inlineStr">
@@ -7157,12 +7163,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ30" s="3"/>
+      <c r="AZ30" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN002</t>
+          <t>26四川港投MTN002</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7172,7 +7180,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102683841.IB</t>
+          <t>102683849.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7181,55 +7189,55 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>24.1</v>
+        <v>41.1</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>25四川港投MTN001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.19Y</t>
+          <t>3.30Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.7758</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>四川省港航投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B 52.36</t>
+          <t>C 29.17</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7239,12 +7247,12 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -7253,17 +7261,19 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V31" s="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7274,17 +7284,17 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为24亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金</t>
+          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7295,7 +7305,7 @@
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7305,7 +7315,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第二期中期票据</t>
+          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7340,32 +7350,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7400,7 +7410,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN002</t>
+          <t>26厦门市政MTN002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7410,19 +7420,19 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683855.IB</t>
+          <t>102683853.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -7430,29 +7440,29 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>29.1</v>
+        <v>23.98</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26厦门航空MTN001(可持续挂钩)</t>
+          <t>26厦门市政MTN001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>2.51Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6600</t>
+          <t>1.6057</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7462,12 +7472,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司</t>
+          <t>厦门市政集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>B- 37.15</t>
+          <t>C+ 31.75</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7477,12 +7487,12 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 11:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -7491,17 +7501,19 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V32" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7517,12 +7529,12 @@
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额6亿元,拟用于支付飞机采购预付款和补充发行人本部及子公司营运资金需求。</t>
+          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7533,7 +7545,7 @@
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7543,7 +7555,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>厦门航空有限公司2026年度第二期中期票据</t>
+          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7553,14 +7565,10 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -7578,32 +7586,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7631,12 +7639,14 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26桂铁投MTN002</t>
+          <t>26凤城河MTN005</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7646,64 +7656,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683852.IB</t>
+          <t>102683842.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>30.98</v>
+        <v>39.1</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26桂铁07</t>
+          <t>26凤城河MTN004</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+2.00Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.7092</t>
+          <t>1.7018</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>1.6950/1.6900</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>泰州凤城河建设发展有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.19</t>
+          <t>C- 20.43</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7713,12 +7723,12 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 10:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7727,40 +7737,40 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.5273</v>
+        <v>3.8333</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>32.0</v>
+        <v>1.25</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额11亿元,募集资金拟用于偿还发行人2026年10月4日到期兑付的"26桂铁投SCP001"本金11亿元[26桂铁投SCP001]</t>
+          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中信银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7781,7 +7791,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年度第二期中期票据</t>
+          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7791,10 +7801,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -7817,7 +7831,7 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7827,12 +7841,12 @@
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
@@ -7842,7 +7856,7 @@
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7852,7 +7866,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7872,7 +7886,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26四川港投MTN002</t>
+          <t>26创元投资MTN002</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7882,64 +7896,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683849.IB</t>
+          <t>102683846.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.60 ~ 2.00</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>41.1</v>
+        <v>30.98</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25四川港投MTN001</t>
+          <t>26创元投资MTN001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>3.30Y</t>
+          <t>4.93Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7758</t>
+          <t>1.8136</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>1.8300/1.7700</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司</t>
+          <t>苏州创元投资发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C 27.92</t>
+          <t>C- 13.00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7949,12 +7963,12 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7963,19 +7977,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.2</v>
+        <v>4.0</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7986,17 +8000,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据计划发行5.00亿元,拟全部用于偿还发行人到期有息债务。[23四川港投MTN001]</t>
+          <t>发行人本期债务融资工具发行金额2.50亿元,募集资金拟全部用于发行人本部偿还有息负债</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,成都农村商业银行股份有限公司</t>
+          <t>南京银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -8017,7 +8031,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>四川省港航投资集团有限责任公司2026年度第二期中期票据</t>
+          <t>苏州创元投资发展(集团)有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8027,14 +8041,10 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休9</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8052,7 +8062,7 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
@@ -8067,12 +8077,12 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
@@ -8112,7 +8122,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN002</t>
+          <t>26越秀集团MTN007</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8122,64 +8132,64 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683853.IB</t>
+          <t>102683847.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.55 ~ 1.85</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>23.98</v>
+        <v>35.1</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26厦门市政MTN001</t>
+          <t>24越秀集团MTN007(绿色)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6057</t>
+          <t>1.6850</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7050/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C- 24.86</t>
+          <t>B- 36.66</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8189,12 +8199,12 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-28 11:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -8203,19 +8213,17 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>1.02</v>
-      </c>
+        <v>1.8143</v>
+      </c>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8226,17 +8234,17 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据8亿元,拟用于偿还发行人即将到期的债务融资工具。[26厦门市政SCP001]</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信证券股份有限公司</t>
+          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -8257,7 +8265,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>厦门市政集团有限公司2026年度第二期中期票据</t>
+          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8267,10 +8275,14 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8288,12 +8300,12 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
@@ -8303,17 +8315,17 @@
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8341,14 +8353,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ35" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ35" s="3"/>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN005</t>
+          <t>26越秀集团MTN006</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8358,7 +8368,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683842.IB</t>
+          <t>102683856.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -8367,55 +8377,55 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.55 ~ 1.85</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>39.1</v>
+        <v>35.1</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26凤城河MTN004</t>
+          <t>24越秀集团MTN007(绿色)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.99Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7018</t>
+          <t>1.6850</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.6950/1.6900</t>
+          <t>1.7050/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>广州越秀集团股份有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 20.08</t>
+          <t>B- 36.66</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8425,12 +8435,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-28 10:00</t>
+          <t>09-28 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8439,14 +8449,14 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>3.8333</v>
+        <v>1.6857</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -8456,23 +8466,23 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行金额为3亿元,用于偿还发行人存量债务融资工具[26凤城河SCP002]</t>
+          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8493,7 +8503,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年度第五期中期票据</t>
+          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8528,32 +8538,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8581,14 +8591,12 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AZ36" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ36" s="3"/>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26创元投资MTN002</t>
+          <t>26晋中公用MTN003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8598,64 +8606,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102683846.IB</t>
+          <t>102683857.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.5</v>
+        <v>2.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2.5</v>
+        <v>2.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.00</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
         <v>1.72</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>30.98</v>
+        <v>43.1</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26创元投资MTN001</t>
+          <t>26晋中01</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.93Y</t>
+          <t>2.82Y+2.00Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.8136</t>
+          <t>1.7164</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.8300/1.7700</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>苏州创元投资发展(集团)有限公司</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 12.77</t>
+          <t>D+ 6.72</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8679,40 +8687,38 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>山西省-晋中市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额2.50亿元,募集资金拟全部用于发行人本部偿还有息负债</t>
+          <t>本期中期票据拟发行金额2亿元,用于偿还发行人本部的债务融资工具本金。[23晋中公用MTN002]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,招商银行股份有限公司</t>
+          <t>招商银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8733,7 +8739,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>苏州创元投资发展(集团)有限公司2026年度第二期中期票据</t>
+          <t>晋中市公用基础设施投资控股(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8743,10 +8749,14 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t>2026-09-30</t>
@@ -8764,7 +8774,7 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
@@ -8779,17 +8789,17 @@
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8818,23 +8828,23 @@
         </is>
       </c>
       <c r="AZ37" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN007</t>
+          <t>26龙翔01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102683847.IB</t>
+          <t>520506.SZ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8843,55 +8853,55 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 1.85</t>
+          <t>2.20 ~ 2.90</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>35.1</v>
+        <v>91.1</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24越秀集团MTN007(绿色)</t>
+          <t>25射阳02</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>3.39Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>1.7968</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.7050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>龙翔投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 37.63</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8901,7 +8911,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8911,48 +8921,52 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1.8143</v>
+        <v>4.05</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.28%~2.38%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还公司债券[23龙翔01]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>广州农村商业银行股份有限公司,宁波银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD38" s="3"/>
+          <t>恒泰长财证券有限责任公司,甬兴证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr">
+        <is>
+          <t>长春新区发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8962,72 +8976,72 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第七期中期票据(浮息债券)</t>
+          <t>龙翔投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="AK38" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休8</t>
         </is>
       </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>生物制品</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9037,7 +9051,7 @@
       </c>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW38" s="3" t="inlineStr">
@@ -9060,17 +9074,17 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26越秀集团MTN006</t>
+          <t>26滨江04</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-28 18:00</t>
+          <t>09-28 19:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102683856.IB</t>
+          <t>284047.SH</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -9079,55 +9093,55 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>7.0</v>
+        <v>9.7</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>7.0</v>
+        <v>9.7</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 1.85</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>35.1</v>
+        <v>36.1</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24越秀集团MTN007(绿色)</t>
+          <t>24滨江投资PPN003</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.6850</t>
+          <t>1.6778</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.7050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司</t>
+          <t>南京滨江投资发展有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 37.63</t>
+          <t>C- 17.00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9137,33 +9151,31 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-28 09:00</t>
+          <t>09-28 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>1.6857</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.1</v>
-      </c>
+        <v>3.31</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9174,23 +9186,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本期中期票据募集资金7亿元用于偿还发行人有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23滨江06]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,江苏银行股份有限公司</t>
+          <t>南京证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9200,72 +9212,72 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>广州越秀集团股份有限公司2026年度第六期中期票据(浮息债券)</t>
+          <t>南京滨江投资发展有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="AK39" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休8</t>
         </is>
       </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-28.xlsx
+++ b/data/credit_bond_all_2026-09-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-01" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
     </row>
